--- a/output/graficos_nacionales/plot_nacional_e_rezjov_a_2023.xlsx
+++ b/output/graficos_nacionales/plot_nacional_e_rezjov_a_2023.xlsx
@@ -15129,7 +15129,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Rezago respecto a la población de 6 a 21 años</t>
+          <t>Por comunas</t>
         </is>
       </c>
     </row>

--- a/output/graficos_nacionales/plot_nacional_e_rezjov_a_2023.xlsx
+++ b/output/graficos_nacionales/plot_nacional_e_rezjov_a_2023.xlsx
@@ -416,7 +416,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Aysén</t>
+          <t>Aysen</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -462,7 +462,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Aysén</t>
+          <t>Aysen</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -508,7 +508,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Aysén</t>
+          <t>Aysen</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -554,7 +554,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Aysén</t>
+          <t>Aysen</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -600,7 +600,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Aysén</t>
+          <t>Aysen</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -646,7 +646,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Aysén</t>
+          <t>Aysen</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -692,7 +692,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Aysén</t>
+          <t>Aysen</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -738,7 +738,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Aysén</t>
+          <t>Aysen</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -922,7 +922,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Aysén</t>
+          <t>Aysen</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -1106,7 +1106,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Valparaiso</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -1152,7 +1152,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Valparaiso</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -1290,7 +1290,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Valparaiso</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -1382,7 +1382,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Valparaiso</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -1566,7 +1566,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Valparaiso</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -1796,7 +1796,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Valparaiso</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -2026,7 +2026,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Valparaiso</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -2072,7 +2072,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Valparaiso</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -2210,7 +2210,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Valparaiso</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -2348,7 +2348,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Valparaiso</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -2486,7 +2486,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Valparaiso</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -2670,7 +2670,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Valparaiso</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -2946,7 +2946,7 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Valparaiso</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -3360,7 +3360,7 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Valparaiso</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
@@ -3452,7 +3452,7 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Valparaiso</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
@@ -3820,7 +3820,7 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Ñuble</t>
+          <t>Nuble</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
@@ -4050,7 +4050,7 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Ñuble</t>
+          <t>Nuble</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
@@ -4188,7 +4188,7 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Valparaiso</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
@@ -4234,7 +4234,7 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Valparaiso</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
@@ -4372,7 +4372,7 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Ñuble</t>
+          <t>Nuble</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
@@ -4510,7 +4510,7 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Valparaiso</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
@@ -4556,7 +4556,7 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Valparaiso</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
@@ -4878,7 +4878,7 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Valparaiso</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
@@ -5016,7 +5016,7 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Valparaiso</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
@@ -5062,7 +5062,7 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Valparaiso</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
@@ -5108,7 +5108,7 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Ñuble</t>
+          <t>Nuble</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
@@ -5154,7 +5154,7 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Ñuble</t>
+          <t>Nuble</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
@@ -5246,7 +5246,7 @@
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Valparaiso</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
@@ -5522,7 +5522,7 @@
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Valparaiso</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
@@ -5614,7 +5614,7 @@
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Ñuble</t>
+          <t>Nuble</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
@@ -5660,7 +5660,7 @@
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Ñuble</t>
+          <t>Nuble</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
@@ -5798,7 +5798,7 @@
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Valparaiso</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
@@ -5844,7 +5844,7 @@
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>Ñuble</t>
+          <t>Nuble</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
@@ -6028,7 +6028,7 @@
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>Ñuble</t>
+          <t>Nuble</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
@@ -6074,7 +6074,7 @@
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>Ñuble</t>
+          <t>Nuble</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
@@ -6120,7 +6120,7 @@
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>Ñuble</t>
+          <t>Nuble</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
@@ -6166,7 +6166,7 @@
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>Ñuble</t>
+          <t>Nuble</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
@@ -6304,7 +6304,7 @@
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Valparaiso</t>
         </is>
       </c>
       <c r="D130" t="inlineStr">
@@ -6442,7 +6442,7 @@
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Valparaiso</t>
         </is>
       </c>
       <c r="D133" t="inlineStr">
@@ -6488,7 +6488,7 @@
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Valparaiso</t>
         </is>
       </c>
       <c r="D134" t="inlineStr">
@@ -6534,7 +6534,7 @@
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Valparaiso</t>
         </is>
       </c>
       <c r="D135" t="inlineStr">
@@ -6580,7 +6580,7 @@
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Valparaiso</t>
         </is>
       </c>
       <c r="D136" t="inlineStr">
@@ -7040,7 +7040,7 @@
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Valparaiso</t>
         </is>
       </c>
       <c r="D146" t="inlineStr">
@@ -7224,7 +7224,7 @@
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Valparaiso</t>
         </is>
       </c>
       <c r="D150" t="inlineStr">
@@ -7500,7 +7500,7 @@
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>Ñuble</t>
+          <t>Nuble</t>
         </is>
       </c>
       <c r="D156" t="inlineStr">
@@ -7684,7 +7684,7 @@
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>Ñuble</t>
+          <t>Nuble</t>
         </is>
       </c>
       <c r="D160" t="inlineStr">
@@ -7868,7 +7868,7 @@
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Valparaiso</t>
         </is>
       </c>
       <c r="D164" t="inlineStr">
@@ -8052,7 +8052,7 @@
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t>Ñuble</t>
+          <t>Nuble</t>
         </is>
       </c>
       <c r="D168" t="inlineStr">
@@ -8144,7 +8144,7 @@
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>Ñuble</t>
+          <t>Nuble</t>
         </is>
       </c>
       <c r="D170" t="inlineStr">
@@ -8328,7 +8328,7 @@
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t>Ñuble</t>
+          <t>Nuble</t>
         </is>
       </c>
       <c r="D174" t="inlineStr">
@@ -8420,7 +8420,7 @@
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t>Ñuble</t>
+          <t>Nuble</t>
         </is>
       </c>
       <c r="D176" t="inlineStr">
@@ -8558,7 +8558,7 @@
       </c>
       <c r="C179" t="inlineStr">
         <is>
-          <t>Ñuble</t>
+          <t>Nuble</t>
         </is>
       </c>
       <c r="D179" t="inlineStr">
@@ -8650,7 +8650,7 @@
       </c>
       <c r="C181" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Valparaiso</t>
         </is>
       </c>
       <c r="D181" t="inlineStr">
@@ -8696,7 +8696,7 @@
       </c>
       <c r="C182" t="inlineStr">
         <is>
-          <t>Tarapacá</t>
+          <t>Tarapaca</t>
         </is>
       </c>
       <c r="D182" t="inlineStr">
@@ -8834,7 +8834,7 @@
       </c>
       <c r="C185" t="inlineStr">
         <is>
-          <t>Tarapacá</t>
+          <t>Tarapaca</t>
         </is>
       </c>
       <c r="D185" t="inlineStr">
@@ -9064,7 +9064,7 @@
       </c>
       <c r="C190" t="inlineStr">
         <is>
-          <t>Tarapacá</t>
+          <t>Tarapaca</t>
         </is>
       </c>
       <c r="D190" t="inlineStr">
@@ -9110,7 +9110,7 @@
       </c>
       <c r="C191" t="inlineStr">
         <is>
-          <t>Tarapacá</t>
+          <t>Tarapaca</t>
         </is>
       </c>
       <c r="D191" t="inlineStr">
@@ -9156,7 +9156,7 @@
       </c>
       <c r="C192" t="inlineStr">
         <is>
-          <t>Tarapacá</t>
+          <t>Tarapaca</t>
         </is>
       </c>
       <c r="D192" t="inlineStr">
@@ -9570,7 +9570,7 @@
       </c>
       <c r="C201" t="inlineStr">
         <is>
-          <t>Tarapacá</t>
+          <t>Tarapaca</t>
         </is>
       </c>
       <c r="D201" t="inlineStr">
@@ -10398,7 +10398,7 @@
       </c>
       <c r="C219" t="inlineStr">
         <is>
-          <t>Tarapacá</t>
+          <t>Tarapaca</t>
         </is>
       </c>
       <c r="D219" t="inlineStr">
@@ -10444,7 +10444,7 @@
       </c>
       <c r="C220" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Biobio</t>
         </is>
       </c>
       <c r="D220" t="inlineStr">
@@ -10536,7 +10536,7 @@
       </c>
       <c r="C222" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Biobio</t>
         </is>
       </c>
       <c r="D222" t="inlineStr">
@@ -10628,7 +10628,7 @@
       </c>
       <c r="C224" t="inlineStr">
         <is>
-          <t>La Araucanía</t>
+          <t>La Araucania</t>
         </is>
       </c>
       <c r="D224" t="inlineStr">
@@ -10674,7 +10674,7 @@
       </c>
       <c r="C225" t="inlineStr">
         <is>
-          <t>La Araucanía</t>
+          <t>La Araucania</t>
         </is>
       </c>
       <c r="D225" t="inlineStr">
@@ -10812,7 +10812,7 @@
       </c>
       <c r="C228" t="inlineStr">
         <is>
-          <t>La Araucanía</t>
+          <t>La Araucania</t>
         </is>
       </c>
       <c r="D228" t="inlineStr">
@@ -10996,7 +10996,7 @@
       </c>
       <c r="C232" t="inlineStr">
         <is>
-          <t>La Araucanía</t>
+          <t>La Araucania</t>
         </is>
       </c>
       <c r="D232" t="inlineStr">
@@ -11042,7 +11042,7 @@
       </c>
       <c r="C233" t="inlineStr">
         <is>
-          <t>La Araucanía</t>
+          <t>La Araucania</t>
         </is>
       </c>
       <c r="D233" t="inlineStr">
@@ -11134,7 +11134,7 @@
       </c>
       <c r="C235" t="inlineStr">
         <is>
-          <t>Los Ríos</t>
+          <t>Los Rios</t>
         </is>
       </c>
       <c r="D235" t="inlineStr">
@@ -11226,7 +11226,7 @@
       </c>
       <c r="C237" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Biobio</t>
         </is>
       </c>
       <c r="D237" t="inlineStr">
@@ -11318,7 +11318,7 @@
       </c>
       <c r="C239" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Biobio</t>
         </is>
       </c>
       <c r="D239" t="inlineStr">
@@ -11364,7 +11364,7 @@
       </c>
       <c r="C240" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Biobio</t>
         </is>
       </c>
       <c r="D240" t="inlineStr">
@@ -11456,7 +11456,7 @@
       </c>
       <c r="C242" t="inlineStr">
         <is>
-          <t>Los Ríos</t>
+          <t>Los Rios</t>
         </is>
       </c>
       <c r="D242" t="inlineStr">
@@ -11548,7 +11548,7 @@
       </c>
       <c r="C244" t="inlineStr">
         <is>
-          <t>La Araucanía</t>
+          <t>La Araucania</t>
         </is>
       </c>
       <c r="D244" t="inlineStr">
@@ -11594,7 +11594,7 @@
       </c>
       <c r="C245" t="inlineStr">
         <is>
-          <t>La Araucanía</t>
+          <t>La Araucania</t>
         </is>
       </c>
       <c r="D245" t="inlineStr">
@@ -11686,7 +11686,7 @@
       </c>
       <c r="C247" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Biobio</t>
         </is>
       </c>
       <c r="D247" t="inlineStr">
@@ -11778,7 +11778,7 @@
       </c>
       <c r="C249" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Biobio</t>
         </is>
       </c>
       <c r="D249" t="inlineStr">
@@ -11824,7 +11824,7 @@
       </c>
       <c r="C250" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Biobio</t>
         </is>
       </c>
       <c r="D250" t="inlineStr">
@@ -11916,7 +11916,7 @@
       </c>
       <c r="C252" t="inlineStr">
         <is>
-          <t>La Araucanía</t>
+          <t>La Araucania</t>
         </is>
       </c>
       <c r="D252" t="inlineStr">
@@ -11962,7 +11962,7 @@
       </c>
       <c r="C253" t="inlineStr">
         <is>
-          <t>La Araucanía</t>
+          <t>La Araucania</t>
         </is>
       </c>
       <c r="D253" t="inlineStr">
@@ -12008,7 +12008,7 @@
       </c>
       <c r="C254" t="inlineStr">
         <is>
-          <t>Los Ríos</t>
+          <t>Los Rios</t>
         </is>
       </c>
       <c r="D254" t="inlineStr">
@@ -12054,7 +12054,7 @@
       </c>
       <c r="C255" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Biobio</t>
         </is>
       </c>
       <c r="D255" t="inlineStr">
@@ -12100,7 +12100,7 @@
       </c>
       <c r="C256" t="inlineStr">
         <is>
-          <t>Los Ríos</t>
+          <t>Los Rios</t>
         </is>
       </c>
       <c r="D256" t="inlineStr">
@@ -12284,7 +12284,7 @@
       </c>
       <c r="C260" t="inlineStr">
         <is>
-          <t>La Araucanía</t>
+          <t>La Araucania</t>
         </is>
       </c>
       <c r="D260" t="inlineStr">
@@ -12330,7 +12330,7 @@
       </c>
       <c r="C261" t="inlineStr">
         <is>
-          <t>La Araucanía</t>
+          <t>La Araucania</t>
         </is>
       </c>
       <c r="D261" t="inlineStr">
@@ -12376,7 +12376,7 @@
       </c>
       <c r="C262" t="inlineStr">
         <is>
-          <t>Los Ríos</t>
+          <t>Los Rios</t>
         </is>
       </c>
       <c r="D262" t="inlineStr">
@@ -12422,7 +12422,7 @@
       </c>
       <c r="C263" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Biobio</t>
         </is>
       </c>
       <c r="D263" t="inlineStr">
@@ -12468,7 +12468,7 @@
       </c>
       <c r="C264" t="inlineStr">
         <is>
-          <t>La Araucanía</t>
+          <t>La Araucania</t>
         </is>
       </c>
       <c r="D264" t="inlineStr">
@@ -12560,7 +12560,7 @@
       </c>
       <c r="C266" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Biobio</t>
         </is>
       </c>
       <c r="D266" t="inlineStr">
@@ -12652,7 +12652,7 @@
       </c>
       <c r="C268" t="inlineStr">
         <is>
-          <t>La Araucanía</t>
+          <t>La Araucania</t>
         </is>
       </c>
       <c r="D268" t="inlineStr">
@@ -12698,7 +12698,7 @@
       </c>
       <c r="C269" t="inlineStr">
         <is>
-          <t>La Araucanía</t>
+          <t>La Araucania</t>
         </is>
       </c>
       <c r="D269" t="inlineStr">
@@ -12790,7 +12790,7 @@
       </c>
       <c r="C271" t="inlineStr">
         <is>
-          <t>La Araucanía</t>
+          <t>La Araucania</t>
         </is>
       </c>
       <c r="D271" t="inlineStr">
@@ -12882,7 +12882,7 @@
       </c>
       <c r="C273" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Biobio</t>
         </is>
       </c>
       <c r="D273" t="inlineStr">
@@ -12928,7 +12928,7 @@
       </c>
       <c r="C274" t="inlineStr">
         <is>
-          <t>La Araucanía</t>
+          <t>La Araucania</t>
         </is>
       </c>
       <c r="D274" t="inlineStr">
@@ -12974,7 +12974,7 @@
       </c>
       <c r="C275" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Biobio</t>
         </is>
       </c>
       <c r="D275" t="inlineStr">
@@ -13020,7 +13020,7 @@
       </c>
       <c r="C276" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Biobio</t>
         </is>
       </c>
       <c r="D276" t="inlineStr">
@@ -13066,7 +13066,7 @@
       </c>
       <c r="C277" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Biobio</t>
         </is>
       </c>
       <c r="D277" t="inlineStr">
@@ -13112,7 +13112,7 @@
       </c>
       <c r="C278" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Biobio</t>
         </is>
       </c>
       <c r="D278" t="inlineStr">
@@ -13158,7 +13158,7 @@
       </c>
       <c r="C279" t="inlineStr">
         <is>
-          <t>La Araucanía</t>
+          <t>La Araucania</t>
         </is>
       </c>
       <c r="D279" t="inlineStr">
@@ -13250,7 +13250,7 @@
       </c>
       <c r="C281" t="inlineStr">
         <is>
-          <t>La Araucanía</t>
+          <t>La Araucania</t>
         </is>
       </c>
       <c r="D281" t="inlineStr">
@@ -13296,7 +13296,7 @@
       </c>
       <c r="C282" t="inlineStr">
         <is>
-          <t>La Araucanía</t>
+          <t>La Araucania</t>
         </is>
       </c>
       <c r="D282" t="inlineStr">
@@ -13342,7 +13342,7 @@
       </c>
       <c r="C283" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Biobio</t>
         </is>
       </c>
       <c r="D283" t="inlineStr">
@@ -13526,7 +13526,7 @@
       </c>
       <c r="C287" t="inlineStr">
         <is>
-          <t>La Araucanía</t>
+          <t>La Araucania</t>
         </is>
       </c>
       <c r="D287" t="inlineStr">
@@ -13572,7 +13572,7 @@
       </c>
       <c r="C288" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Biobio</t>
         </is>
       </c>
       <c r="D288" t="inlineStr">
@@ -13618,7 +13618,7 @@
       </c>
       <c r="C289" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Biobio</t>
         </is>
       </c>
       <c r="D289" t="inlineStr">
@@ -13664,7 +13664,7 @@
       </c>
       <c r="C290" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Biobio</t>
         </is>
       </c>
       <c r="D290" t="inlineStr">
@@ -13710,7 +13710,7 @@
       </c>
       <c r="C291" t="inlineStr">
         <is>
-          <t>La Araucanía</t>
+          <t>La Araucania</t>
         </is>
       </c>
       <c r="D291" t="inlineStr">
@@ -13802,7 +13802,7 @@
       </c>
       <c r="C293" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Biobio</t>
         </is>
       </c>
       <c r="D293" t="inlineStr">
@@ -13848,7 +13848,7 @@
       </c>
       <c r="C294" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Biobio</t>
         </is>
       </c>
       <c r="D294" t="inlineStr">
@@ -13894,7 +13894,7 @@
       </c>
       <c r="C295" t="inlineStr">
         <is>
-          <t>La Araucanía</t>
+          <t>La Araucania</t>
         </is>
       </c>
       <c r="D295" t="inlineStr">
@@ -13986,7 +13986,7 @@
       </c>
       <c r="C297" t="inlineStr">
         <is>
-          <t>La Araucanía</t>
+          <t>La Araucania</t>
         </is>
       </c>
       <c r="D297" t="inlineStr">
@@ -14032,7 +14032,7 @@
       </c>
       <c r="C298" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Biobio</t>
         </is>
       </c>
       <c r="D298" t="inlineStr">
@@ -14078,7 +14078,7 @@
       </c>
       <c r="C299" t="inlineStr">
         <is>
-          <t>La Araucanía</t>
+          <t>La Araucania</t>
         </is>
       </c>
       <c r="D299" t="inlineStr">
@@ -14124,7 +14124,7 @@
       </c>
       <c r="C300" t="inlineStr">
         <is>
-          <t>La Araucanía</t>
+          <t>La Araucania</t>
         </is>
       </c>
       <c r="D300" t="inlineStr">
@@ -14170,7 +14170,7 @@
       </c>
       <c r="C301" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Biobio</t>
         </is>
       </c>
       <c r="D301" t="inlineStr">
@@ -14262,7 +14262,7 @@
       </c>
       <c r="C303" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Biobio</t>
         </is>
       </c>
       <c r="D303" t="inlineStr">
@@ -14308,7 +14308,7 @@
       </c>
       <c r="C304" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Biobio</t>
         </is>
       </c>
       <c r="D304" t="inlineStr">
@@ -14354,7 +14354,7 @@
       </c>
       <c r="C305" t="inlineStr">
         <is>
-          <t>La Araucanía</t>
+          <t>La Araucania</t>
         </is>
       </c>
       <c r="D305" t="inlineStr">
@@ -14400,7 +14400,7 @@
       </c>
       <c r="C306" t="inlineStr">
         <is>
-          <t>Los Ríos</t>
+          <t>Los Rios</t>
         </is>
       </c>
       <c r="D306" t="inlineStr">
@@ -14446,7 +14446,7 @@
       </c>
       <c r="C307" t="inlineStr">
         <is>
-          <t>La Araucanía</t>
+          <t>La Araucania</t>
         </is>
       </c>
       <c r="D307" t="inlineStr">
@@ -14492,7 +14492,7 @@
       </c>
       <c r="C308" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Biobio</t>
         </is>
       </c>
       <c r="D308" t="inlineStr">
@@ -14538,7 +14538,7 @@
       </c>
       <c r="C309" t="inlineStr">
         <is>
-          <t>La Araucanía</t>
+          <t>La Araucania</t>
         </is>
       </c>
       <c r="D309" t="inlineStr">
@@ -14584,7 +14584,7 @@
       </c>
       <c r="C310" t="inlineStr">
         <is>
-          <t>Los Ríos</t>
+          <t>Los Rios</t>
         </is>
       </c>
       <c r="D310" t="inlineStr">
@@ -14630,7 +14630,7 @@
       </c>
       <c r="C311" t="inlineStr">
         <is>
-          <t>Los Ríos</t>
+          <t>Los Rios</t>
         </is>
       </c>
       <c r="D311" t="inlineStr">
@@ -14676,7 +14676,7 @@
       </c>
       <c r="C312" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Biobio</t>
         </is>
       </c>
       <c r="D312" t="inlineStr">
@@ -14722,7 +14722,7 @@
       </c>
       <c r="C313" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Biobio</t>
         </is>
       </c>
       <c r="D313" t="inlineStr">
@@ -14768,7 +14768,7 @@
       </c>
       <c r="C314" t="inlineStr">
         <is>
-          <t>La Araucanía</t>
+          <t>La Araucania</t>
         </is>
       </c>
       <c r="D314" t="inlineStr">
@@ -14814,7 +14814,7 @@
       </c>
       <c r="C315" t="inlineStr">
         <is>
-          <t>Los Ríos</t>
+          <t>Los Rios</t>
         </is>
       </c>
       <c r="D315" t="inlineStr">
@@ -14860,7 +14860,7 @@
       </c>
       <c r="C316" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Biobio</t>
         </is>
       </c>
       <c r="D316" t="inlineStr">
@@ -14952,7 +14952,7 @@
       </c>
       <c r="C318" t="inlineStr">
         <is>
-          <t>La Araucanía</t>
+          <t>La Araucania</t>
         </is>
       </c>
       <c r="D318" t="inlineStr">
@@ -14998,7 +14998,7 @@
       </c>
       <c r="C319" t="inlineStr">
         <is>
-          <t>La Araucanía</t>
+          <t>La Araucania</t>
         </is>
       </c>
       <c r="D319" t="inlineStr">
@@ -15044,7 +15044,7 @@
       </c>
       <c r="C320" t="inlineStr">
         <is>
-          <t>La Araucanía</t>
+          <t>La Araucania</t>
         </is>
       </c>
       <c r="D320" t="inlineStr">
@@ -15090,7 +15090,7 @@
       </c>
       <c r="C321" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Biobio</t>
         </is>
       </c>
       <c r="D321" t="inlineStr">
@@ -15136,7 +15136,7 @@
       </c>
       <c r="C322" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Biobio</t>
         </is>
       </c>
       <c r="D322" t="inlineStr">
@@ -15182,7 +15182,7 @@
       </c>
       <c r="C323" t="inlineStr">
         <is>
-          <t>Los Ríos</t>
+          <t>Los Rios</t>
         </is>
       </c>
       <c r="D323" t="inlineStr">
@@ -15228,7 +15228,7 @@
       </c>
       <c r="C324" t="inlineStr">
         <is>
-          <t>Los Ríos</t>
+          <t>Los Rios</t>
         </is>
       </c>
       <c r="D324" t="inlineStr">
@@ -15274,7 +15274,7 @@
       </c>
       <c r="C325" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Biobio</t>
         </is>
       </c>
       <c r="D325" t="inlineStr">

--- a/output/graficos_nacionales/plot_nacional_e_rezjov_a_2023.xlsx
+++ b/output/graficos_nacionales/plot_nacional_e_rezjov_a_2023.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="697" uniqueCount="697">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="694" uniqueCount="694">
   <si>
     <t xml:space="preserve">year</t>
   </si>
@@ -1324,15 +1324,6 @@
     <t xml:space="preserve">Ovalle</t>
   </si>
   <si>
-    <t xml:space="preserve">Arica y Parinacota</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15101</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Arica</t>
-  </si>
-  <si>
     <t xml:space="preserve">2203</t>
   </si>
   <si>
@@ -2062,7 +2053,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-07-30 15:41</t>
+    <t xml:space="preserve">2026-09-07 12:58</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
@@ -2474,7 +2465,7 @@
   <cols>
     <col min="1" max="1" width="10.71" hidden="0" customWidth="1"/>
     <col min="2" max="2" width="11.71" hidden="0" customWidth="1"/>
-    <col min="3" max="3" width="20.71" hidden="0" customWidth="1"/>
+    <col min="3" max="3" width="15.71" hidden="0" customWidth="1"/>
     <col min="4" max="4" width="12.71" hidden="0" customWidth="1"/>
     <col min="5" max="5" width="22.71" hidden="0" customWidth="1"/>
     <col min="6" max="6" width="14.71" hidden="0" customWidth="1"/>
@@ -9081,16 +9072,16 @@
         <v>2023</v>
       </c>
       <c r="B207" s="2" t="n">
-        <v>15</v>
+        <v>2</v>
       </c>
       <c r="C207" s="2" t="s">
+        <v>396</v>
+      </c>
+      <c r="D207" s="2" t="s">
         <v>435</v>
       </c>
-      <c r="D207" s="2" t="s">
+      <c r="E207" s="2" t="s">
         <v>436</v>
-      </c>
-      <c r="E207" s="2" t="s">
-        <v>437</v>
       </c>
       <c r="F207" s="2" t="s">
         <v>384</v>
@@ -9102,7 +9093,7 @@
         <v>15</v>
       </c>
       <c r="I207" s="2" t="n">
-        <v>1.62</v>
+        <v>1.6</v>
       </c>
       <c r="J207" s="2" t="s">
         <v>15</v>
@@ -9113,16 +9104,16 @@
         <v>2023</v>
       </c>
       <c r="B208" s="2" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="C208" s="2" t="s">
-        <v>396</v>
+        <v>389</v>
       </c>
       <c r="D208" s="2" t="s">
+        <v>437</v>
+      </c>
+      <c r="E208" s="2" t="s">
         <v>438</v>
-      </c>
-      <c r="E208" s="2" t="s">
-        <v>439</v>
       </c>
       <c r="F208" s="2" t="s">
         <v>384</v>
@@ -9134,7 +9125,7 @@
         <v>15</v>
       </c>
       <c r="I208" s="2" t="n">
-        <v>1.6</v>
+        <v>1.42</v>
       </c>
       <c r="J208" s="2" t="s">
         <v>15</v>
@@ -9145,16 +9136,16 @@
         <v>2023</v>
       </c>
       <c r="B209" s="2" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C209" s="2" t="s">
-        <v>389</v>
+        <v>386</v>
       </c>
       <c r="D209" s="2" t="s">
+        <v>439</v>
+      </c>
+      <c r="E209" s="2" t="s">
         <v>440</v>
-      </c>
-      <c r="E209" s="2" t="s">
-        <v>441</v>
       </c>
       <c r="F209" s="2" t="s">
         <v>384</v>
@@ -9166,7 +9157,7 @@
         <v>15</v>
       </c>
       <c r="I209" s="2" t="n">
-        <v>1.42</v>
+        <v>1.37</v>
       </c>
       <c r="J209" s="2" t="s">
         <v>15</v>
@@ -9183,10 +9174,10 @@
         <v>386</v>
       </c>
       <c r="D210" s="2" t="s">
+        <v>441</v>
+      </c>
+      <c r="E210" s="2" t="s">
         <v>442</v>
-      </c>
-      <c r="E210" s="2" t="s">
-        <v>443</v>
       </c>
       <c r="F210" s="2" t="s">
         <v>384</v>
@@ -9198,7 +9189,7 @@
         <v>15</v>
       </c>
       <c r="I210" s="2" t="n">
-        <v>1.37</v>
+        <v>1.3</v>
       </c>
       <c r="J210" s="2" t="s">
         <v>15</v>
@@ -9209,16 +9200,16 @@
         <v>2023</v>
       </c>
       <c r="B211" s="2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C211" s="2" t="s">
-        <v>386</v>
+        <v>389</v>
       </c>
       <c r="D211" s="2" t="s">
+        <v>443</v>
+      </c>
+      <c r="E211" s="2" t="s">
         <v>444</v>
-      </c>
-      <c r="E211" s="2" t="s">
-        <v>445</v>
       </c>
       <c r="F211" s="2" t="s">
         <v>384</v>
@@ -9241,16 +9232,16 @@
         <v>2023</v>
       </c>
       <c r="B212" s="2" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C212" s="2" t="s">
-        <v>389</v>
+        <v>386</v>
       </c>
       <c r="D212" s="2" t="s">
+        <v>445</v>
+      </c>
+      <c r="E212" s="2" t="s">
         <v>446</v>
-      </c>
-      <c r="E212" s="2" t="s">
-        <v>447</v>
       </c>
       <c r="F212" s="2" t="s">
         <v>384</v>
@@ -9262,7 +9253,7 @@
         <v>15</v>
       </c>
       <c r="I212" s="2" t="n">
-        <v>1.3</v>
+        <v>1.25</v>
       </c>
       <c r="J212" s="2" t="s">
         <v>15</v>
@@ -9273,16 +9264,16 @@
         <v>2023</v>
       </c>
       <c r="B213" s="2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C213" s="2" t="s">
-        <v>386</v>
+        <v>389</v>
       </c>
       <c r="D213" s="2" t="s">
+        <v>447</v>
+      </c>
+      <c r="E213" s="2" t="s">
         <v>448</v>
-      </c>
-      <c r="E213" s="2" t="s">
-        <v>449</v>
       </c>
       <c r="F213" s="2" t="s">
         <v>384</v>
@@ -9294,7 +9285,7 @@
         <v>15</v>
       </c>
       <c r="I213" s="2" t="n">
-        <v>1.25</v>
+        <v>1.14</v>
       </c>
       <c r="J213" s="2" t="s">
         <v>15</v>
@@ -9311,10 +9302,10 @@
         <v>389</v>
       </c>
       <c r="D214" s="2" t="s">
+        <v>449</v>
+      </c>
+      <c r="E214" s="2" t="s">
         <v>450</v>
-      </c>
-      <c r="E214" s="2" t="s">
-        <v>451</v>
       </c>
       <c r="F214" s="2" t="s">
         <v>384</v>
@@ -9326,7 +9317,7 @@
         <v>15</v>
       </c>
       <c r="I214" s="2" t="n">
-        <v>1.14</v>
+        <v>1.08</v>
       </c>
       <c r="J214" s="2" t="s">
         <v>15</v>
@@ -9343,10 +9334,10 @@
         <v>389</v>
       </c>
       <c r="D215" s="2" t="s">
+        <v>451</v>
+      </c>
+      <c r="E215" s="2" t="s">
         <v>452</v>
-      </c>
-      <c r="E215" s="2" t="s">
-        <v>453</v>
       </c>
       <c r="F215" s="2" t="s">
         <v>384</v>
@@ -9358,7 +9349,7 @@
         <v>15</v>
       </c>
       <c r="I215" s="2" t="n">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="J215" s="2" t="s">
         <v>15</v>
@@ -9375,10 +9366,10 @@
         <v>389</v>
       </c>
       <c r="D216" s="2" t="s">
+        <v>453</v>
+      </c>
+      <c r="E216" s="2" t="s">
         <v>454</v>
-      </c>
-      <c r="E216" s="2" t="s">
-        <v>455</v>
       </c>
       <c r="F216" s="2" t="s">
         <v>384</v>
@@ -9401,16 +9392,16 @@
         <v>2023</v>
       </c>
       <c r="B217" s="2" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C217" s="2" t="s">
-        <v>389</v>
+        <v>396</v>
       </c>
       <c r="D217" s="2" t="s">
+        <v>455</v>
+      </c>
+      <c r="E217" s="2" t="s">
         <v>456</v>
-      </c>
-      <c r="E217" s="2" t="s">
-        <v>457</v>
       </c>
       <c r="F217" s="2" t="s">
         <v>384</v>
@@ -9422,7 +9413,7 @@
         <v>15</v>
       </c>
       <c r="I217" s="2" t="n">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="J217" s="2" t="s">
         <v>15</v>
@@ -9433,16 +9424,16 @@
         <v>2023</v>
       </c>
       <c r="B218" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C218" s="2" t="s">
-        <v>396</v>
+        <v>381</v>
       </c>
       <c r="D218" s="2" t="s">
+        <v>457</v>
+      </c>
+      <c r="E218" s="2" t="s">
         <v>458</v>
-      </c>
-      <c r="E218" s="2" t="s">
-        <v>459</v>
       </c>
       <c r="F218" s="2" t="s">
         <v>384</v>
@@ -9454,7 +9445,7 @@
         <v>15</v>
       </c>
       <c r="I218" s="2" t="n">
-        <v>1.06</v>
+        <v>0.92</v>
       </c>
       <c r="J218" s="2" t="s">
         <v>15</v>
@@ -9465,10 +9456,10 @@
         <v>2023</v>
       </c>
       <c r="B219" s="2" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="C219" s="2" t="s">
-        <v>381</v>
+        <v>459</v>
       </c>
       <c r="D219" s="2" t="s">
         <v>460</v>
@@ -9477,16 +9468,16 @@
         <v>461</v>
       </c>
       <c r="F219" s="2" t="s">
-        <v>384</v>
+        <v>462</v>
       </c>
       <c r="G219" s="2" t="s">
-        <v>385</v>
+        <v>463</v>
       </c>
       <c r="H219" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I219" s="2" t="n">
-        <v>0.92</v>
+        <v>5.13</v>
       </c>
       <c r="J219" s="2" t="s">
         <v>15</v>
@@ -9497,28 +9488,28 @@
         <v>2023</v>
       </c>
       <c r="B220" s="2" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="C220" s="2" t="s">
+        <v>464</v>
+      </c>
+      <c r="D220" s="2" t="s">
+        <v>465</v>
+      </c>
+      <c r="E220" s="2" t="s">
+        <v>466</v>
+      </c>
+      <c r="F220" s="2" t="s">
         <v>462</v>
       </c>
-      <c r="D220" s="2" t="s">
+      <c r="G220" s="2" t="s">
         <v>463</v>
       </c>
-      <c r="E220" s="2" t="s">
-        <v>464</v>
-      </c>
-      <c r="F220" s="2" t="s">
-        <v>465</v>
-      </c>
-      <c r="G220" s="2" t="s">
-        <v>466</v>
-      </c>
       <c r="H220" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I220" s="2" t="n">
-        <v>5.13</v>
+        <v>4.13</v>
       </c>
       <c r="J220" s="2" t="s">
         <v>15</v>
@@ -9529,28 +9520,28 @@
         <v>2023</v>
       </c>
       <c r="B221" s="2" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="C221" s="2" t="s">
+        <v>459</v>
+      </c>
+      <c r="D221" s="2" t="s">
         <v>467</v>
       </c>
-      <c r="D221" s="2" t="s">
+      <c r="E221" s="2" t="s">
         <v>468</v>
       </c>
-      <c r="E221" s="2" t="s">
-        <v>469</v>
-      </c>
       <c r="F221" s="2" t="s">
-        <v>465</v>
+        <v>462</v>
       </c>
       <c r="G221" s="2" t="s">
-        <v>466</v>
+        <v>463</v>
       </c>
       <c r="H221" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I221" s="2" t="n">
-        <v>4.13</v>
+        <v>3.71</v>
       </c>
       <c r="J221" s="2" t="s">
         <v>15</v>
@@ -9561,28 +9552,28 @@
         <v>2023</v>
       </c>
       <c r="B222" s="2" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="C222" s="2" t="s">
+        <v>464</v>
+      </c>
+      <c r="D222" s="2" t="s">
+        <v>469</v>
+      </c>
+      <c r="E222" s="2" t="s">
+        <v>470</v>
+      </c>
+      <c r="F222" s="2" t="s">
         <v>462</v>
       </c>
-      <c r="D222" s="2" t="s">
-        <v>470</v>
-      </c>
-      <c r="E222" s="2" t="s">
-        <v>471</v>
-      </c>
-      <c r="F222" s="2" t="s">
-        <v>465</v>
-      </c>
       <c r="G222" s="2" t="s">
-        <v>466</v>
+        <v>463</v>
       </c>
       <c r="H222" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I222" s="2" t="n">
-        <v>3.71</v>
+        <v>3.7</v>
       </c>
       <c r="J222" s="2" t="s">
         <v>15</v>
@@ -9593,10 +9584,10 @@
         <v>2023</v>
       </c>
       <c r="B223" s="2" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C223" s="2" t="s">
-        <v>467</v>
+        <v>471</v>
       </c>
       <c r="D223" s="2" t="s">
         <v>472</v>
@@ -9605,16 +9596,16 @@
         <v>473</v>
       </c>
       <c r="F223" s="2" t="s">
-        <v>465</v>
+        <v>462</v>
       </c>
       <c r="G223" s="2" t="s">
-        <v>466</v>
+        <v>463</v>
       </c>
       <c r="H223" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I223" s="2" t="n">
-        <v>3.7</v>
+        <v>3.56</v>
       </c>
       <c r="J223" s="2" t="s">
         <v>15</v>
@@ -9628,25 +9619,25 @@
         <v>9</v>
       </c>
       <c r="C224" s="2" t="s">
+        <v>471</v>
+      </c>
+      <c r="D224" s="2" t="s">
         <v>474</v>
       </c>
-      <c r="D224" s="2" t="s">
+      <c r="E224" s="2" t="s">
         <v>475</v>
       </c>
-      <c r="E224" s="2" t="s">
-        <v>476</v>
-      </c>
       <c r="F224" s="2" t="s">
-        <v>465</v>
+        <v>462</v>
       </c>
       <c r="G224" s="2" t="s">
-        <v>466</v>
+        <v>463</v>
       </c>
       <c r="H224" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I224" s="2" t="n">
-        <v>3.56</v>
+        <v>3.42</v>
       </c>
       <c r="J224" s="2" t="s">
         <v>15</v>
@@ -9657,28 +9648,28 @@
         <v>2023</v>
       </c>
       <c r="B225" s="2" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C225" s="2" t="s">
-        <v>474</v>
+        <v>464</v>
       </c>
       <c r="D225" s="2" t="s">
+        <v>476</v>
+      </c>
+      <c r="E225" s="2" t="s">
         <v>477</v>
       </c>
-      <c r="E225" s="2" t="s">
-        <v>478</v>
-      </c>
       <c r="F225" s="2" t="s">
-        <v>465</v>
+        <v>462</v>
       </c>
       <c r="G225" s="2" t="s">
-        <v>466</v>
+        <v>463</v>
       </c>
       <c r="H225" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I225" s="2" t="n">
-        <v>3.42</v>
+        <v>3.24</v>
       </c>
       <c r="J225" s="2" t="s">
         <v>15</v>
@@ -9692,25 +9683,25 @@
         <v>10</v>
       </c>
       <c r="C226" s="2" t="s">
-        <v>467</v>
+        <v>464</v>
       </c>
       <c r="D226" s="2" t="s">
+        <v>478</v>
+      </c>
+      <c r="E226" s="2" t="s">
         <v>479</v>
       </c>
-      <c r="E226" s="2" t="s">
-        <v>480</v>
-      </c>
       <c r="F226" s="2" t="s">
-        <v>465</v>
+        <v>462</v>
       </c>
       <c r="G226" s="2" t="s">
-        <v>466</v>
+        <v>463</v>
       </c>
       <c r="H226" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I226" s="2" t="n">
-        <v>3.24</v>
+        <v>3.06</v>
       </c>
       <c r="J226" s="2" t="s">
         <v>15</v>
@@ -9721,28 +9712,28 @@
         <v>2023</v>
       </c>
       <c r="B227" s="2" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C227" s="2" t="s">
-        <v>467</v>
+        <v>471</v>
       </c>
       <c r="D227" s="2" t="s">
+        <v>480</v>
+      </c>
+      <c r="E227" s="2" t="s">
         <v>481</v>
       </c>
-      <c r="E227" s="2" t="s">
-        <v>482</v>
-      </c>
       <c r="F227" s="2" t="s">
-        <v>465</v>
+        <v>462</v>
       </c>
       <c r="G227" s="2" t="s">
-        <v>466</v>
+        <v>463</v>
       </c>
       <c r="H227" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I227" s="2" t="n">
-        <v>3.06</v>
+        <v>2.94</v>
       </c>
       <c r="J227" s="2" t="s">
         <v>15</v>
@@ -9753,28 +9744,28 @@
         <v>2023</v>
       </c>
       <c r="B228" s="2" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C228" s="2" t="s">
-        <v>474</v>
+        <v>464</v>
       </c>
       <c r="D228" s="2" t="s">
+        <v>482</v>
+      </c>
+      <c r="E228" s="2" t="s">
         <v>483</v>
       </c>
-      <c r="E228" s="2" t="s">
-        <v>484</v>
-      </c>
       <c r="F228" s="2" t="s">
-        <v>465</v>
+        <v>462</v>
       </c>
       <c r="G228" s="2" t="s">
-        <v>466</v>
+        <v>463</v>
       </c>
       <c r="H228" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I228" s="2" t="n">
-        <v>2.94</v>
+        <v>2.89</v>
       </c>
       <c r="J228" s="2" t="s">
         <v>15</v>
@@ -9788,25 +9779,25 @@
         <v>10</v>
       </c>
       <c r="C229" s="2" t="s">
-        <v>467</v>
+        <v>464</v>
       </c>
       <c r="D229" s="2" t="s">
+        <v>484</v>
+      </c>
+      <c r="E229" s="2" t="s">
         <v>485</v>
       </c>
-      <c r="E229" s="2" t="s">
-        <v>486</v>
-      </c>
       <c r="F229" s="2" t="s">
-        <v>465</v>
+        <v>462</v>
       </c>
       <c r="G229" s="2" t="s">
-        <v>466</v>
+        <v>463</v>
       </c>
       <c r="H229" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I229" s="2" t="n">
-        <v>2.89</v>
+        <v>2.88</v>
       </c>
       <c r="J229" s="2" t="s">
         <v>15</v>
@@ -9820,25 +9811,25 @@
         <v>10</v>
       </c>
       <c r="C230" s="2" t="s">
-        <v>467</v>
+        <v>464</v>
       </c>
       <c r="D230" s="2" t="s">
+        <v>486</v>
+      </c>
+      <c r="E230" s="2" t="s">
         <v>487</v>
       </c>
-      <c r="E230" s="2" t="s">
-        <v>488</v>
-      </c>
       <c r="F230" s="2" t="s">
-        <v>465</v>
+        <v>462</v>
       </c>
       <c r="G230" s="2" t="s">
-        <v>466</v>
+        <v>463</v>
       </c>
       <c r="H230" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I230" s="2" t="n">
-        <v>2.88</v>
+        <v>2.75</v>
       </c>
       <c r="J230" s="2" t="s">
         <v>15</v>
@@ -9849,28 +9840,28 @@
         <v>2023</v>
       </c>
       <c r="B231" s="2" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C231" s="2" t="s">
-        <v>467</v>
+        <v>471</v>
       </c>
       <c r="D231" s="2" t="s">
+        <v>488</v>
+      </c>
+      <c r="E231" s="2" t="s">
         <v>489</v>
       </c>
-      <c r="E231" s="2" t="s">
-        <v>490</v>
-      </c>
       <c r="F231" s="2" t="s">
-        <v>465</v>
+        <v>462</v>
       </c>
       <c r="G231" s="2" t="s">
-        <v>466</v>
+        <v>463</v>
       </c>
       <c r="H231" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I231" s="2" t="n">
-        <v>2.75</v>
+        <v>2.71</v>
       </c>
       <c r="J231" s="2" t="s">
         <v>15</v>
@@ -9884,25 +9875,25 @@
         <v>9</v>
       </c>
       <c r="C232" s="2" t="s">
-        <v>474</v>
+        <v>471</v>
       </c>
       <c r="D232" s="2" t="s">
+        <v>490</v>
+      </c>
+      <c r="E232" s="2" t="s">
         <v>491</v>
       </c>
-      <c r="E232" s="2" t="s">
-        <v>492</v>
-      </c>
       <c r="F232" s="2" t="s">
-        <v>465</v>
+        <v>462</v>
       </c>
       <c r="G232" s="2" t="s">
-        <v>466</v>
+        <v>463</v>
       </c>
       <c r="H232" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I232" s="2" t="n">
-        <v>2.71</v>
+        <v>2.62</v>
       </c>
       <c r="J232" s="2" t="s">
         <v>15</v>
@@ -9913,10 +9904,10 @@
         <v>2023</v>
       </c>
       <c r="B233" s="2" t="n">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="C233" s="2" t="s">
-        <v>474</v>
+        <v>492</v>
       </c>
       <c r="D233" s="2" t="s">
         <v>493</v>
@@ -9925,16 +9916,16 @@
         <v>494</v>
       </c>
       <c r="F233" s="2" t="s">
-        <v>465</v>
+        <v>462</v>
       </c>
       <c r="G233" s="2" t="s">
-        <v>466</v>
+        <v>463</v>
       </c>
       <c r="H233" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I233" s="2" t="n">
-        <v>2.62</v>
+        <v>2.57</v>
       </c>
       <c r="J233" s="2" t="s">
         <v>15</v>
@@ -9945,22 +9936,22 @@
         <v>2023</v>
       </c>
       <c r="B234" s="2" t="n">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="C234" s="2" t="s">
+        <v>464</v>
+      </c>
+      <c r="D234" s="2" t="s">
         <v>495</v>
       </c>
-      <c r="D234" s="2" t="s">
+      <c r="E234" s="2" t="s">
         <v>496</v>
       </c>
-      <c r="E234" s="2" t="s">
-        <v>497</v>
-      </c>
       <c r="F234" s="2" t="s">
-        <v>465</v>
+        <v>462</v>
       </c>
       <c r="G234" s="2" t="s">
-        <v>466</v>
+        <v>463</v>
       </c>
       <c r="H234" s="2" t="s">
         <v>15</v>
@@ -9980,25 +9971,25 @@
         <v>10</v>
       </c>
       <c r="C235" s="2" t="s">
-        <v>467</v>
+        <v>464</v>
       </c>
       <c r="D235" s="2" t="s">
+        <v>497</v>
+      </c>
+      <c r="E235" s="2" t="s">
         <v>498</v>
       </c>
-      <c r="E235" s="2" t="s">
-        <v>499</v>
-      </c>
       <c r="F235" s="2" t="s">
-        <v>465</v>
+        <v>462</v>
       </c>
       <c r="G235" s="2" t="s">
-        <v>466</v>
+        <v>463</v>
       </c>
       <c r="H235" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I235" s="2" t="n">
-        <v>2.57</v>
+        <v>2.53</v>
       </c>
       <c r="J235" s="2" t="s">
         <v>15</v>
@@ -10009,28 +10000,28 @@
         <v>2023</v>
       </c>
       <c r="B236" s="2" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="C236" s="2" t="s">
-        <v>467</v>
+        <v>459</v>
       </c>
       <c r="D236" s="2" t="s">
+        <v>499</v>
+      </c>
+      <c r="E236" s="2" t="s">
         <v>500</v>
       </c>
-      <c r="E236" s="2" t="s">
-        <v>501</v>
-      </c>
       <c r="F236" s="2" t="s">
-        <v>465</v>
+        <v>462</v>
       </c>
       <c r="G236" s="2" t="s">
-        <v>466</v>
+        <v>463</v>
       </c>
       <c r="H236" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I236" s="2" t="n">
-        <v>2.53</v>
+        <v>2.5</v>
       </c>
       <c r="J236" s="2" t="s">
         <v>15</v>
@@ -10041,28 +10032,28 @@
         <v>2023</v>
       </c>
       <c r="B237" s="2" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="C237" s="2" t="s">
+        <v>464</v>
+      </c>
+      <c r="D237" s="2" t="s">
+        <v>501</v>
+      </c>
+      <c r="E237" s="2" t="s">
+        <v>502</v>
+      </c>
+      <c r="F237" s="2" t="s">
         <v>462</v>
       </c>
-      <c r="D237" s="2" t="s">
-        <v>502</v>
-      </c>
-      <c r="E237" s="2" t="s">
-        <v>503</v>
-      </c>
-      <c r="F237" s="2" t="s">
-        <v>465</v>
-      </c>
       <c r="G237" s="2" t="s">
-        <v>466</v>
+        <v>463</v>
       </c>
       <c r="H237" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I237" s="2" t="n">
-        <v>2.5</v>
+        <v>2.45</v>
       </c>
       <c r="J237" s="2" t="s">
         <v>15</v>
@@ -10073,28 +10064,28 @@
         <v>2023</v>
       </c>
       <c r="B238" s="2" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="C238" s="2" t="s">
-        <v>467</v>
+        <v>459</v>
       </c>
       <c r="D238" s="2" t="s">
+        <v>503</v>
+      </c>
+      <c r="E238" s="2" t="s">
         <v>504</v>
       </c>
-      <c r="E238" s="2" t="s">
-        <v>505</v>
-      </c>
       <c r="F238" s="2" t="s">
-        <v>465</v>
+        <v>462</v>
       </c>
       <c r="G238" s="2" t="s">
-        <v>466</v>
+        <v>463</v>
       </c>
       <c r="H238" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I238" s="2" t="n">
-        <v>2.45</v>
+        <v>2.43</v>
       </c>
       <c r="J238" s="2" t="s">
         <v>15</v>
@@ -10108,19 +10099,19 @@
         <v>8</v>
       </c>
       <c r="C239" s="2" t="s">
+        <v>459</v>
+      </c>
+      <c r="D239" s="2" t="s">
+        <v>505</v>
+      </c>
+      <c r="E239" s="2" t="s">
+        <v>506</v>
+      </c>
+      <c r="F239" s="2" t="s">
         <v>462</v>
       </c>
-      <c r="D239" s="2" t="s">
-        <v>506</v>
-      </c>
-      <c r="E239" s="2" t="s">
-        <v>507</v>
-      </c>
-      <c r="F239" s="2" t="s">
-        <v>465</v>
-      </c>
       <c r="G239" s="2" t="s">
-        <v>466</v>
+        <v>463</v>
       </c>
       <c r="H239" s="2" t="s">
         <v>15</v>
@@ -10137,22 +10128,22 @@
         <v>2023</v>
       </c>
       <c r="B240" s="2" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="C240" s="2" t="s">
+        <v>464</v>
+      </c>
+      <c r="D240" s="2" t="s">
+        <v>507</v>
+      </c>
+      <c r="E240" s="2" t="s">
+        <v>508</v>
+      </c>
+      <c r="F240" s="2" t="s">
         <v>462</v>
       </c>
-      <c r="D240" s="2" t="s">
-        <v>508</v>
-      </c>
-      <c r="E240" s="2" t="s">
-        <v>509</v>
-      </c>
-      <c r="F240" s="2" t="s">
-        <v>465</v>
-      </c>
       <c r="G240" s="2" t="s">
-        <v>466</v>
+        <v>463</v>
       </c>
       <c r="H240" s="2" t="s">
         <v>15</v>
@@ -10169,28 +10160,28 @@
         <v>2023</v>
       </c>
       <c r="B241" s="2" t="n">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="C241" s="2" t="s">
-        <v>467</v>
+        <v>492</v>
       </c>
       <c r="D241" s="2" t="s">
+        <v>509</v>
+      </c>
+      <c r="E241" s="2" t="s">
         <v>510</v>
       </c>
-      <c r="E241" s="2" t="s">
-        <v>511</v>
-      </c>
       <c r="F241" s="2" t="s">
-        <v>465</v>
+        <v>462</v>
       </c>
       <c r="G241" s="2" t="s">
-        <v>466</v>
+        <v>463</v>
       </c>
       <c r="H241" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I241" s="2" t="n">
-        <v>2.43</v>
+        <v>2.41</v>
       </c>
       <c r="J241" s="2" t="s">
         <v>15</v>
@@ -10201,22 +10192,22 @@
         <v>2023</v>
       </c>
       <c r="B242" s="2" t="n">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="C242" s="2" t="s">
-        <v>495</v>
+        <v>464</v>
       </c>
       <c r="D242" s="2" t="s">
+        <v>511</v>
+      </c>
+      <c r="E242" s="2" t="s">
         <v>512</v>
       </c>
-      <c r="E242" s="2" t="s">
-        <v>513</v>
-      </c>
       <c r="F242" s="2" t="s">
-        <v>465</v>
+        <v>462</v>
       </c>
       <c r="G242" s="2" t="s">
-        <v>466</v>
+        <v>463</v>
       </c>
       <c r="H242" s="2" t="s">
         <v>15</v>
@@ -10233,28 +10224,28 @@
         <v>2023</v>
       </c>
       <c r="B243" s="2" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C243" s="2" t="s">
-        <v>467</v>
+        <v>471</v>
       </c>
       <c r="D243" s="2" t="s">
+        <v>513</v>
+      </c>
+      <c r="E243" s="2" t="s">
         <v>514</v>
       </c>
-      <c r="E243" s="2" t="s">
-        <v>515</v>
-      </c>
       <c r="F243" s="2" t="s">
-        <v>465</v>
+        <v>462</v>
       </c>
       <c r="G243" s="2" t="s">
-        <v>466</v>
+        <v>463</v>
       </c>
       <c r="H243" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I243" s="2" t="n">
-        <v>2.41</v>
+        <v>2.39</v>
       </c>
       <c r="J243" s="2" t="s">
         <v>15</v>
@@ -10268,25 +10259,25 @@
         <v>9</v>
       </c>
       <c r="C244" s="2" t="s">
-        <v>474</v>
+        <v>471</v>
       </c>
       <c r="D244" s="2" t="s">
+        <v>515</v>
+      </c>
+      <c r="E244" s="2" t="s">
         <v>516</v>
       </c>
-      <c r="E244" s="2" t="s">
-        <v>517</v>
-      </c>
       <c r="F244" s="2" t="s">
-        <v>465</v>
+        <v>462</v>
       </c>
       <c r="G244" s="2" t="s">
-        <v>466</v>
+        <v>463</v>
       </c>
       <c r="H244" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I244" s="2" t="n">
-        <v>2.39</v>
+        <v>2.38</v>
       </c>
       <c r="J244" s="2" t="s">
         <v>15</v>
@@ -10297,28 +10288,28 @@
         <v>2023</v>
       </c>
       <c r="B245" s="2" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C245" s="2" t="s">
-        <v>474</v>
+        <v>459</v>
       </c>
       <c r="D245" s="2" t="s">
+        <v>517</v>
+      </c>
+      <c r="E245" s="2" t="s">
         <v>518</v>
       </c>
-      <c r="E245" s="2" t="s">
-        <v>519</v>
-      </c>
       <c r="F245" s="2" t="s">
-        <v>465</v>
+        <v>462</v>
       </c>
       <c r="G245" s="2" t="s">
-        <v>466</v>
+        <v>463</v>
       </c>
       <c r="H245" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I245" s="2" t="n">
-        <v>2.38</v>
+        <v>2.36</v>
       </c>
       <c r="J245" s="2" t="s">
         <v>15</v>
@@ -10329,22 +10320,22 @@
         <v>2023</v>
       </c>
       <c r="B246" s="2" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="C246" s="2" t="s">
+        <v>464</v>
+      </c>
+      <c r="D246" s="2" t="s">
+        <v>519</v>
+      </c>
+      <c r="E246" s="2" t="s">
+        <v>520</v>
+      </c>
+      <c r="F246" s="2" t="s">
         <v>462</v>
       </c>
-      <c r="D246" s="2" t="s">
-        <v>520</v>
-      </c>
-      <c r="E246" s="2" t="s">
-        <v>521</v>
-      </c>
-      <c r="F246" s="2" t="s">
-        <v>465</v>
-      </c>
       <c r="G246" s="2" t="s">
-        <v>466</v>
+        <v>463</v>
       </c>
       <c r="H246" s="2" t="s">
         <v>15</v>
@@ -10364,25 +10355,25 @@
         <v>10</v>
       </c>
       <c r="C247" s="2" t="s">
-        <v>467</v>
+        <v>464</v>
       </c>
       <c r="D247" s="2" t="s">
+        <v>521</v>
+      </c>
+      <c r="E247" s="2" t="s">
         <v>522</v>
       </c>
-      <c r="E247" s="2" t="s">
-        <v>523</v>
-      </c>
       <c r="F247" s="2" t="s">
-        <v>465</v>
+        <v>462</v>
       </c>
       <c r="G247" s="2" t="s">
-        <v>466</v>
+        <v>463</v>
       </c>
       <c r="H247" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I247" s="2" t="n">
-        <v>2.36</v>
+        <v>2.34</v>
       </c>
       <c r="J247" s="2" t="s">
         <v>15</v>
@@ -10393,28 +10384,28 @@
         <v>2023</v>
       </c>
       <c r="B248" s="2" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="C248" s="2" t="s">
-        <v>467</v>
+        <v>459</v>
       </c>
       <c r="D248" s="2" t="s">
+        <v>523</v>
+      </c>
+      <c r="E248" s="2" t="s">
         <v>524</v>
       </c>
-      <c r="E248" s="2" t="s">
-        <v>525</v>
-      </c>
       <c r="F248" s="2" t="s">
-        <v>465</v>
+        <v>462</v>
       </c>
       <c r="G248" s="2" t="s">
-        <v>466</v>
+        <v>463</v>
       </c>
       <c r="H248" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I248" s="2" t="n">
-        <v>2.34</v>
+        <v>2.32</v>
       </c>
       <c r="J248" s="2" t="s">
         <v>15</v>
@@ -10428,25 +10419,25 @@
         <v>8</v>
       </c>
       <c r="C249" s="2" t="s">
+        <v>459</v>
+      </c>
+      <c r="D249" s="2" t="s">
+        <v>525</v>
+      </c>
+      <c r="E249" s="2" t="s">
+        <v>526</v>
+      </c>
+      <c r="F249" s="2" t="s">
         <v>462</v>
       </c>
-      <c r="D249" s="2" t="s">
-        <v>526</v>
-      </c>
-      <c r="E249" s="2" t="s">
-        <v>527</v>
-      </c>
-      <c r="F249" s="2" t="s">
-        <v>465</v>
-      </c>
       <c r="G249" s="2" t="s">
-        <v>466</v>
+        <v>463</v>
       </c>
       <c r="H249" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I249" s="2" t="n">
-        <v>2.32</v>
+        <v>2.31</v>
       </c>
       <c r="J249" s="2" t="s">
         <v>15</v>
@@ -10457,28 +10448,28 @@
         <v>2023</v>
       </c>
       <c r="B250" s="2" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="C250" s="2" t="s">
+        <v>464</v>
+      </c>
+      <c r="D250" s="2" t="s">
+        <v>527</v>
+      </c>
+      <c r="E250" s="2" t="s">
+        <v>528</v>
+      </c>
+      <c r="F250" s="2" t="s">
         <v>462</v>
       </c>
-      <c r="D250" s="2" t="s">
-        <v>528</v>
-      </c>
-      <c r="E250" s="2" t="s">
-        <v>529</v>
-      </c>
-      <c r="F250" s="2" t="s">
-        <v>465</v>
-      </c>
       <c r="G250" s="2" t="s">
-        <v>466</v>
+        <v>463</v>
       </c>
       <c r="H250" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I250" s="2" t="n">
-        <v>2.31</v>
+        <v>2.3</v>
       </c>
       <c r="J250" s="2" t="s">
         <v>15</v>
@@ -10489,28 +10480,28 @@
         <v>2023</v>
       </c>
       <c r="B251" s="2" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C251" s="2" t="s">
-        <v>467</v>
+        <v>471</v>
       </c>
       <c r="D251" s="2" t="s">
+        <v>529</v>
+      </c>
+      <c r="E251" s="2" t="s">
         <v>530</v>
       </c>
-      <c r="E251" s="2" t="s">
-        <v>531</v>
-      </c>
       <c r="F251" s="2" t="s">
-        <v>465</v>
+        <v>462</v>
       </c>
       <c r="G251" s="2" t="s">
-        <v>466</v>
+        <v>463</v>
       </c>
       <c r="H251" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I251" s="2" t="n">
-        <v>2.3</v>
+        <v>2.28</v>
       </c>
       <c r="J251" s="2" t="s">
         <v>15</v>
@@ -10524,25 +10515,25 @@
         <v>9</v>
       </c>
       <c r="C252" s="2" t="s">
-        <v>474</v>
+        <v>471</v>
       </c>
       <c r="D252" s="2" t="s">
+        <v>531</v>
+      </c>
+      <c r="E252" s="2" t="s">
         <v>532</v>
       </c>
-      <c r="E252" s="2" t="s">
-        <v>533</v>
-      </c>
       <c r="F252" s="2" t="s">
-        <v>465</v>
+        <v>462</v>
       </c>
       <c r="G252" s="2" t="s">
-        <v>466</v>
+        <v>463</v>
       </c>
       <c r="H252" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I252" s="2" t="n">
-        <v>2.28</v>
+        <v>2.26</v>
       </c>
       <c r="J252" s="2" t="s">
         <v>15</v>
@@ -10553,28 +10544,28 @@
         <v>2023</v>
       </c>
       <c r="B253" s="2" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C253" s="2" t="s">
-        <v>474</v>
+        <v>459</v>
       </c>
       <c r="D253" s="2" t="s">
+        <v>533</v>
+      </c>
+      <c r="E253" s="2" t="s">
         <v>534</v>
       </c>
-      <c r="E253" s="2" t="s">
-        <v>535</v>
-      </c>
       <c r="F253" s="2" t="s">
-        <v>465</v>
+        <v>462</v>
       </c>
       <c r="G253" s="2" t="s">
-        <v>466</v>
+        <v>463</v>
       </c>
       <c r="H253" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I253" s="2" t="n">
-        <v>2.26</v>
+        <v>2.25</v>
       </c>
       <c r="J253" s="2" t="s">
         <v>15</v>
@@ -10585,22 +10576,22 @@
         <v>2023</v>
       </c>
       <c r="B254" s="2" t="n">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="C254" s="2" t="s">
+        <v>492</v>
+      </c>
+      <c r="D254" s="2" t="s">
+        <v>535</v>
+      </c>
+      <c r="E254" s="2" t="s">
+        <v>536</v>
+      </c>
+      <c r="F254" s="2" t="s">
         <v>462</v>
       </c>
-      <c r="D254" s="2" t="s">
-        <v>536</v>
-      </c>
-      <c r="E254" s="2" t="s">
-        <v>537</v>
-      </c>
-      <c r="F254" s="2" t="s">
-        <v>465</v>
-      </c>
       <c r="G254" s="2" t="s">
-        <v>466</v>
+        <v>463</v>
       </c>
       <c r="H254" s="2" t="s">
         <v>15</v>
@@ -10620,25 +10611,25 @@
         <v>14</v>
       </c>
       <c r="C255" s="2" t="s">
-        <v>495</v>
+        <v>492</v>
       </c>
       <c r="D255" s="2" t="s">
+        <v>537</v>
+      </c>
+      <c r="E255" s="2" t="s">
         <v>538</v>
       </c>
-      <c r="E255" s="2" t="s">
-        <v>539</v>
-      </c>
       <c r="F255" s="2" t="s">
-        <v>465</v>
+        <v>462</v>
       </c>
       <c r="G255" s="2" t="s">
-        <v>466</v>
+        <v>463</v>
       </c>
       <c r="H255" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I255" s="2" t="n">
-        <v>2.25</v>
+        <v>2.22</v>
       </c>
       <c r="J255" s="2" t="s">
         <v>15</v>
@@ -10649,22 +10640,22 @@
         <v>2023</v>
       </c>
       <c r="B256" s="2" t="n">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="C256" s="2" t="s">
-        <v>495</v>
+        <v>464</v>
       </c>
       <c r="D256" s="2" t="s">
+        <v>539</v>
+      </c>
+      <c r="E256" s="2" t="s">
         <v>540</v>
       </c>
-      <c r="E256" s="2" t="s">
-        <v>541</v>
-      </c>
       <c r="F256" s="2" t="s">
-        <v>465</v>
+        <v>462</v>
       </c>
       <c r="G256" s="2" t="s">
-        <v>466</v>
+        <v>463</v>
       </c>
       <c r="H256" s="2" t="s">
         <v>15</v>
@@ -10684,25 +10675,25 @@
         <v>10</v>
       </c>
       <c r="C257" s="2" t="s">
-        <v>467</v>
+        <v>464</v>
       </c>
       <c r="D257" s="2" t="s">
+        <v>541</v>
+      </c>
+      <c r="E257" s="2" t="s">
         <v>542</v>
       </c>
-      <c r="E257" s="2" t="s">
-        <v>543</v>
-      </c>
       <c r="F257" s="2" t="s">
-        <v>465</v>
+        <v>462</v>
       </c>
       <c r="G257" s="2" t="s">
-        <v>466</v>
+        <v>463</v>
       </c>
       <c r="H257" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I257" s="2" t="n">
-        <v>2.22</v>
+        <v>2.21</v>
       </c>
       <c r="J257" s="2" t="s">
         <v>15</v>
@@ -10716,25 +10707,25 @@
         <v>10</v>
       </c>
       <c r="C258" s="2" t="s">
-        <v>467</v>
+        <v>464</v>
       </c>
       <c r="D258" s="2" t="s">
+        <v>543</v>
+      </c>
+      <c r="E258" s="2" t="s">
         <v>544</v>
       </c>
-      <c r="E258" s="2" t="s">
-        <v>545</v>
-      </c>
       <c r="F258" s="2" t="s">
-        <v>465</v>
+        <v>462</v>
       </c>
       <c r="G258" s="2" t="s">
-        <v>466</v>
+        <v>463</v>
       </c>
       <c r="H258" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I258" s="2" t="n">
-        <v>2.21</v>
+        <v>2.2</v>
       </c>
       <c r="J258" s="2" t="s">
         <v>15</v>
@@ -10745,28 +10736,28 @@
         <v>2023</v>
       </c>
       <c r="B259" s="2" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C259" s="2" t="s">
-        <v>467</v>
+        <v>471</v>
       </c>
       <c r="D259" s="2" t="s">
+        <v>545</v>
+      </c>
+      <c r="E259" s="2" t="s">
         <v>546</v>
       </c>
-      <c r="E259" s="2" t="s">
-        <v>547</v>
-      </c>
       <c r="F259" s="2" t="s">
-        <v>465</v>
+        <v>462</v>
       </c>
       <c r="G259" s="2" t="s">
-        <v>466</v>
+        <v>463</v>
       </c>
       <c r="H259" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I259" s="2" t="n">
-        <v>2.2</v>
+        <v>2.18</v>
       </c>
       <c r="J259" s="2" t="s">
         <v>15</v>
@@ -10780,25 +10771,25 @@
         <v>9</v>
       </c>
       <c r="C260" s="2" t="s">
-        <v>474</v>
+        <v>471</v>
       </c>
       <c r="D260" s="2" t="s">
+        <v>547</v>
+      </c>
+      <c r="E260" s="2" t="s">
         <v>548</v>
       </c>
-      <c r="E260" s="2" t="s">
-        <v>549</v>
-      </c>
       <c r="F260" s="2" t="s">
-        <v>465</v>
+        <v>462</v>
       </c>
       <c r="G260" s="2" t="s">
-        <v>466</v>
+        <v>463</v>
       </c>
       <c r="H260" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I260" s="2" t="n">
-        <v>2.18</v>
+        <v>2.17</v>
       </c>
       <c r="J260" s="2" t="s">
         <v>15</v>
@@ -10809,28 +10800,28 @@
         <v>2023</v>
       </c>
       <c r="B261" s="2" t="n">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="C261" s="2" t="s">
-        <v>474</v>
+        <v>492</v>
       </c>
       <c r="D261" s="2" t="s">
+        <v>549</v>
+      </c>
+      <c r="E261" s="2" t="s">
         <v>550</v>
       </c>
-      <c r="E261" s="2" t="s">
-        <v>551</v>
-      </c>
       <c r="F261" s="2" t="s">
-        <v>465</v>
+        <v>462</v>
       </c>
       <c r="G261" s="2" t="s">
-        <v>466</v>
+        <v>463</v>
       </c>
       <c r="H261" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I261" s="2" t="n">
-        <v>2.17</v>
+        <v>2.15</v>
       </c>
       <c r="J261" s="2" t="s">
         <v>15</v>
@@ -10841,28 +10832,28 @@
         <v>2023</v>
       </c>
       <c r="B262" s="2" t="n">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="C262" s="2" t="s">
-        <v>495</v>
+        <v>459</v>
       </c>
       <c r="D262" s="2" t="s">
+        <v>551</v>
+      </c>
+      <c r="E262" s="2" t="s">
         <v>552</v>
       </c>
-      <c r="E262" s="2" t="s">
-        <v>553</v>
-      </c>
       <c r="F262" s="2" t="s">
-        <v>465</v>
+        <v>462</v>
       </c>
       <c r="G262" s="2" t="s">
-        <v>466</v>
+        <v>463</v>
       </c>
       <c r="H262" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I262" s="2" t="n">
-        <v>2.15</v>
+        <v>2.13</v>
       </c>
       <c r="J262" s="2" t="s">
         <v>15</v>
@@ -10873,28 +10864,28 @@
         <v>2023</v>
       </c>
       <c r="B263" s="2" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C263" s="2" t="s">
+        <v>471</v>
+      </c>
+      <c r="D263" s="2" t="s">
+        <v>553</v>
+      </c>
+      <c r="E263" s="2" t="s">
+        <v>554</v>
+      </c>
+      <c r="F263" s="2" t="s">
         <v>462</v>
       </c>
-      <c r="D263" s="2" t="s">
-        <v>554</v>
-      </c>
-      <c r="E263" s="2" t="s">
-        <v>555</v>
-      </c>
-      <c r="F263" s="2" t="s">
-        <v>465</v>
-      </c>
       <c r="G263" s="2" t="s">
-        <v>466</v>
+        <v>463</v>
       </c>
       <c r="H263" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I263" s="2" t="n">
-        <v>2.13</v>
+        <v>2.12</v>
       </c>
       <c r="J263" s="2" t="s">
         <v>15</v>
@@ -10905,28 +10896,28 @@
         <v>2023</v>
       </c>
       <c r="B264" s="2" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C264" s="2" t="s">
-        <v>474</v>
+        <v>459</v>
       </c>
       <c r="D264" s="2" t="s">
+        <v>555</v>
+      </c>
+      <c r="E264" s="2" t="s">
         <v>556</v>
       </c>
-      <c r="E264" s="2" t="s">
-        <v>557</v>
-      </c>
       <c r="F264" s="2" t="s">
-        <v>465</v>
+        <v>462</v>
       </c>
       <c r="G264" s="2" t="s">
-        <v>466</v>
+        <v>463</v>
       </c>
       <c r="H264" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I264" s="2" t="n">
-        <v>2.12</v>
+        <v>2.11</v>
       </c>
       <c r="J264" s="2" t="s">
         <v>15</v>
@@ -10937,22 +10928,22 @@
         <v>2023</v>
       </c>
       <c r="B265" s="2" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="C265" s="2" t="s">
+        <v>464</v>
+      </c>
+      <c r="D265" s="2" t="s">
+        <v>557</v>
+      </c>
+      <c r="E265" s="2" t="s">
+        <v>558</v>
+      </c>
+      <c r="F265" s="2" t="s">
         <v>462</v>
       </c>
-      <c r="D265" s="2" t="s">
-        <v>558</v>
-      </c>
-      <c r="E265" s="2" t="s">
-        <v>559</v>
-      </c>
-      <c r="F265" s="2" t="s">
-        <v>465</v>
-      </c>
       <c r="G265" s="2" t="s">
-        <v>466</v>
+        <v>463</v>
       </c>
       <c r="H265" s="2" t="s">
         <v>15</v>
@@ -10969,28 +10960,28 @@
         <v>2023</v>
       </c>
       <c r="B266" s="2" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C266" s="2" t="s">
-        <v>467</v>
+        <v>471</v>
       </c>
       <c r="D266" s="2" t="s">
+        <v>559</v>
+      </c>
+      <c r="E266" s="2" t="s">
         <v>560</v>
       </c>
-      <c r="E266" s="2" t="s">
-        <v>561</v>
-      </c>
       <c r="F266" s="2" t="s">
-        <v>465</v>
+        <v>462</v>
       </c>
       <c r="G266" s="2" t="s">
-        <v>466</v>
+        <v>463</v>
       </c>
       <c r="H266" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I266" s="2" t="n">
-        <v>2.11</v>
+        <v>2.1</v>
       </c>
       <c r="J266" s="2" t="s">
         <v>15</v>
@@ -11004,19 +10995,19 @@
         <v>9</v>
       </c>
       <c r="C267" s="2" t="s">
-        <v>474</v>
+        <v>471</v>
       </c>
       <c r="D267" s="2" t="s">
+        <v>561</v>
+      </c>
+      <c r="E267" s="2" t="s">
         <v>562</v>
       </c>
-      <c r="E267" s="2" t="s">
-        <v>563</v>
-      </c>
       <c r="F267" s="2" t="s">
-        <v>465</v>
+        <v>462</v>
       </c>
       <c r="G267" s="2" t="s">
-        <v>466</v>
+        <v>463</v>
       </c>
       <c r="H267" s="2" t="s">
         <v>15</v>
@@ -11033,22 +11024,22 @@
         <v>2023</v>
       </c>
       <c r="B268" s="2" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C268" s="2" t="s">
-        <v>474</v>
+        <v>464</v>
       </c>
       <c r="D268" s="2" t="s">
+        <v>563</v>
+      </c>
+      <c r="E268" s="2" t="s">
         <v>564</v>
       </c>
-      <c r="E268" s="2" t="s">
-        <v>565</v>
-      </c>
       <c r="F268" s="2" t="s">
-        <v>465</v>
+        <v>462</v>
       </c>
       <c r="G268" s="2" t="s">
-        <v>466</v>
+        <v>463</v>
       </c>
       <c r="H268" s="2" t="s">
         <v>15</v>
@@ -11068,19 +11059,19 @@
         <v>10</v>
       </c>
       <c r="C269" s="2" t="s">
-        <v>467</v>
+        <v>464</v>
       </c>
       <c r="D269" s="2" t="s">
+        <v>565</v>
+      </c>
+      <c r="E269" s="2" t="s">
         <v>566</v>
       </c>
-      <c r="E269" s="2" t="s">
-        <v>567</v>
-      </c>
       <c r="F269" s="2" t="s">
-        <v>465</v>
+        <v>462</v>
       </c>
       <c r="G269" s="2" t="s">
-        <v>466</v>
+        <v>463</v>
       </c>
       <c r="H269" s="2" t="s">
         <v>15</v>
@@ -11097,28 +11088,28 @@
         <v>2023</v>
       </c>
       <c r="B270" s="2" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C270" s="2" t="s">
-        <v>467</v>
+        <v>471</v>
       </c>
       <c r="D270" s="2" t="s">
+        <v>567</v>
+      </c>
+      <c r="E270" s="2" t="s">
         <v>568</v>
       </c>
-      <c r="E270" s="2" t="s">
-        <v>569</v>
-      </c>
       <c r="F270" s="2" t="s">
-        <v>465</v>
+        <v>462</v>
       </c>
       <c r="G270" s="2" t="s">
-        <v>466</v>
+        <v>463</v>
       </c>
       <c r="H270" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I270" s="2" t="n">
-        <v>2.1</v>
+        <v>2.08</v>
       </c>
       <c r="J270" s="2" t="s">
         <v>15</v>
@@ -11129,22 +11120,22 @@
         <v>2023</v>
       </c>
       <c r="B271" s="2" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C271" s="2" t="s">
-        <v>474</v>
+        <v>464</v>
       </c>
       <c r="D271" s="2" t="s">
+        <v>569</v>
+      </c>
+      <c r="E271" s="2" t="s">
         <v>570</v>
       </c>
-      <c r="E271" s="2" t="s">
-        <v>571</v>
-      </c>
       <c r="F271" s="2" t="s">
-        <v>465</v>
+        <v>462</v>
       </c>
       <c r="G271" s="2" t="s">
-        <v>466</v>
+        <v>463</v>
       </c>
       <c r="H271" s="2" t="s">
         <v>15</v>
@@ -11161,28 +11152,28 @@
         <v>2023</v>
       </c>
       <c r="B272" s="2" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="C272" s="2" t="s">
-        <v>467</v>
+        <v>459</v>
       </c>
       <c r="D272" s="2" t="s">
+        <v>571</v>
+      </c>
+      <c r="E272" s="2" t="s">
         <v>572</v>
       </c>
-      <c r="E272" s="2" t="s">
-        <v>573</v>
-      </c>
       <c r="F272" s="2" t="s">
-        <v>465</v>
+        <v>462</v>
       </c>
       <c r="G272" s="2" t="s">
-        <v>466</v>
+        <v>463</v>
       </c>
       <c r="H272" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I272" s="2" t="n">
-        <v>2.08</v>
+        <v>2.07</v>
       </c>
       <c r="J272" s="2" t="s">
         <v>15</v>
@@ -11193,28 +11184,28 @@
         <v>2023</v>
       </c>
       <c r="B273" s="2" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C273" s="2" t="s">
+        <v>471</v>
+      </c>
+      <c r="D273" s="2" t="s">
+        <v>573</v>
+      </c>
+      <c r="E273" s="2" t="s">
+        <v>574</v>
+      </c>
+      <c r="F273" s="2" t="s">
         <v>462</v>
       </c>
-      <c r="D273" s="2" t="s">
-        <v>574</v>
-      </c>
-      <c r="E273" s="2" t="s">
-        <v>575</v>
-      </c>
-      <c r="F273" s="2" t="s">
-        <v>465</v>
-      </c>
       <c r="G273" s="2" t="s">
-        <v>466</v>
+        <v>463</v>
       </c>
       <c r="H273" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I273" s="2" t="n">
-        <v>2.07</v>
+        <v>2.03</v>
       </c>
       <c r="J273" s="2" t="s">
         <v>15</v>
@@ -11225,28 +11216,28 @@
         <v>2023</v>
       </c>
       <c r="B274" s="2" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C274" s="2" t="s">
-        <v>474</v>
+        <v>459</v>
       </c>
       <c r="D274" s="2" t="s">
+        <v>575</v>
+      </c>
+      <c r="E274" s="2" t="s">
         <v>576</v>
       </c>
-      <c r="E274" s="2" t="s">
-        <v>577</v>
-      </c>
       <c r="F274" s="2" t="s">
-        <v>465</v>
+        <v>462</v>
       </c>
       <c r="G274" s="2" t="s">
-        <v>466</v>
+        <v>463</v>
       </c>
       <c r="H274" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I274" s="2" t="n">
-        <v>2.03</v>
+        <v>1.99</v>
       </c>
       <c r="J274" s="2" t="s">
         <v>15</v>
@@ -11260,25 +11251,25 @@
         <v>8</v>
       </c>
       <c r="C275" s="2" t="s">
+        <v>459</v>
+      </c>
+      <c r="D275" s="2" t="s">
+        <v>577</v>
+      </c>
+      <c r="E275" s="2" t="s">
+        <v>578</v>
+      </c>
+      <c r="F275" s="2" t="s">
         <v>462</v>
       </c>
-      <c r="D275" s="2" t="s">
-        <v>578</v>
-      </c>
-      <c r="E275" s="2" t="s">
-        <v>579</v>
-      </c>
-      <c r="F275" s="2" t="s">
-        <v>465</v>
-      </c>
       <c r="G275" s="2" t="s">
-        <v>466</v>
+        <v>463</v>
       </c>
       <c r="H275" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I275" s="2" t="n">
-        <v>1.99</v>
+        <v>1.98</v>
       </c>
       <c r="J275" s="2" t="s">
         <v>15</v>
@@ -11292,19 +11283,19 @@
         <v>8</v>
       </c>
       <c r="C276" s="2" t="s">
+        <v>459</v>
+      </c>
+      <c r="D276" s="2" t="s">
+        <v>579</v>
+      </c>
+      <c r="E276" s="2" t="s">
+        <v>580</v>
+      </c>
+      <c r="F276" s="2" t="s">
         <v>462</v>
       </c>
-      <c r="D276" s="2" t="s">
-        <v>580</v>
-      </c>
-      <c r="E276" s="2" t="s">
-        <v>581</v>
-      </c>
-      <c r="F276" s="2" t="s">
-        <v>465</v>
-      </c>
       <c r="G276" s="2" t="s">
-        <v>466</v>
+        <v>463</v>
       </c>
       <c r="H276" s="2" t="s">
         <v>15</v>
@@ -11324,25 +11315,25 @@
         <v>8</v>
       </c>
       <c r="C277" s="2" t="s">
+        <v>459</v>
+      </c>
+      <c r="D277" s="2" t="s">
+        <v>581</v>
+      </c>
+      <c r="E277" s="2" t="s">
+        <v>582</v>
+      </c>
+      <c r="F277" s="2" t="s">
         <v>462</v>
       </c>
-      <c r="D277" s="2" t="s">
-        <v>582</v>
-      </c>
-      <c r="E277" s="2" t="s">
-        <v>583</v>
-      </c>
-      <c r="F277" s="2" t="s">
-        <v>465</v>
-      </c>
       <c r="G277" s="2" t="s">
-        <v>466</v>
+        <v>463</v>
       </c>
       <c r="H277" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I277" s="2" t="n">
-        <v>1.98</v>
+        <v>1.95</v>
       </c>
       <c r="J277" s="2" t="s">
         <v>15</v>
@@ -11353,28 +11344,28 @@
         <v>2023</v>
       </c>
       <c r="B278" s="2" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C278" s="2" t="s">
+        <v>471</v>
+      </c>
+      <c r="D278" s="2" t="s">
+        <v>583</v>
+      </c>
+      <c r="E278" s="2" t="s">
+        <v>584</v>
+      </c>
+      <c r="F278" s="2" t="s">
         <v>462</v>
       </c>
-      <c r="D278" s="2" t="s">
-        <v>584</v>
-      </c>
-      <c r="E278" s="2" t="s">
-        <v>585</v>
-      </c>
-      <c r="F278" s="2" t="s">
-        <v>465</v>
-      </c>
       <c r="G278" s="2" t="s">
-        <v>466</v>
+        <v>463</v>
       </c>
       <c r="H278" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I278" s="2" t="n">
-        <v>1.95</v>
+        <v>1.93</v>
       </c>
       <c r="J278" s="2" t="s">
         <v>15</v>
@@ -11385,28 +11376,28 @@
         <v>2023</v>
       </c>
       <c r="B279" s="2" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C279" s="2" t="s">
-        <v>474</v>
+        <v>464</v>
       </c>
       <c r="D279" s="2" t="s">
+        <v>585</v>
+      </c>
+      <c r="E279" s="2" t="s">
         <v>586</v>
       </c>
-      <c r="E279" s="2" t="s">
-        <v>587</v>
-      </c>
       <c r="F279" s="2" t="s">
-        <v>465</v>
+        <v>462</v>
       </c>
       <c r="G279" s="2" t="s">
-        <v>466</v>
+        <v>463</v>
       </c>
       <c r="H279" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I279" s="2" t="n">
-        <v>1.93</v>
+        <v>1.91</v>
       </c>
       <c r="J279" s="2" t="s">
         <v>15</v>
@@ -11417,28 +11408,28 @@
         <v>2023</v>
       </c>
       <c r="B280" s="2" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C280" s="2" t="s">
-        <v>467</v>
+        <v>471</v>
       </c>
       <c r="D280" s="2" t="s">
+        <v>587</v>
+      </c>
+      <c r="E280" s="2" t="s">
         <v>588</v>
       </c>
-      <c r="E280" s="2" t="s">
-        <v>589</v>
-      </c>
       <c r="F280" s="2" t="s">
-        <v>465</v>
+        <v>462</v>
       </c>
       <c r="G280" s="2" t="s">
-        <v>466</v>
+        <v>463</v>
       </c>
       <c r="H280" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I280" s="2" t="n">
-        <v>1.91</v>
+        <v>1.9</v>
       </c>
       <c r="J280" s="2" t="s">
         <v>15</v>
@@ -11452,25 +11443,25 @@
         <v>9</v>
       </c>
       <c r="C281" s="2" t="s">
-        <v>474</v>
+        <v>471</v>
       </c>
       <c r="D281" s="2" t="s">
+        <v>589</v>
+      </c>
+      <c r="E281" s="2" t="s">
         <v>590</v>
       </c>
-      <c r="E281" s="2" t="s">
-        <v>591</v>
-      </c>
       <c r="F281" s="2" t="s">
-        <v>465</v>
+        <v>462</v>
       </c>
       <c r="G281" s="2" t="s">
-        <v>466</v>
+        <v>463</v>
       </c>
       <c r="H281" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I281" s="2" t="n">
-        <v>1.9</v>
+        <v>1.86</v>
       </c>
       <c r="J281" s="2" t="s">
         <v>15</v>
@@ -11481,28 +11472,28 @@
         <v>2023</v>
       </c>
       <c r="B282" s="2" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C282" s="2" t="s">
-        <v>474</v>
+        <v>459</v>
       </c>
       <c r="D282" s="2" t="s">
+        <v>591</v>
+      </c>
+      <c r="E282" s="2" t="s">
         <v>592</v>
       </c>
-      <c r="E282" s="2" t="s">
-        <v>593</v>
-      </c>
       <c r="F282" s="2" t="s">
-        <v>465</v>
+        <v>462</v>
       </c>
       <c r="G282" s="2" t="s">
-        <v>466</v>
+        <v>463</v>
       </c>
       <c r="H282" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I282" s="2" t="n">
-        <v>1.86</v>
+        <v>1.85</v>
       </c>
       <c r="J282" s="2" t="s">
         <v>15</v>
@@ -11513,22 +11504,22 @@
         <v>2023</v>
       </c>
       <c r="B283" s="2" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="C283" s="2" t="s">
+        <v>464</v>
+      </c>
+      <c r="D283" s="2" t="s">
+        <v>593</v>
+      </c>
+      <c r="E283" s="2" t="s">
+        <v>594</v>
+      </c>
+      <c r="F283" s="2" t="s">
         <v>462</v>
       </c>
-      <c r="D283" s="2" t="s">
-        <v>594</v>
-      </c>
-      <c r="E283" s="2" t="s">
-        <v>595</v>
-      </c>
-      <c r="F283" s="2" t="s">
-        <v>465</v>
-      </c>
       <c r="G283" s="2" t="s">
-        <v>466</v>
+        <v>463</v>
       </c>
       <c r="H283" s="2" t="s">
         <v>15</v>
@@ -11548,25 +11539,25 @@
         <v>10</v>
       </c>
       <c r="C284" s="2" t="s">
-        <v>467</v>
+        <v>464</v>
       </c>
       <c r="D284" s="2" t="s">
+        <v>595</v>
+      </c>
+      <c r="E284" s="2" t="s">
         <v>596</v>
       </c>
-      <c r="E284" s="2" t="s">
-        <v>597</v>
-      </c>
       <c r="F284" s="2" t="s">
-        <v>465</v>
+        <v>462</v>
       </c>
       <c r="G284" s="2" t="s">
-        <v>466</v>
+        <v>463</v>
       </c>
       <c r="H284" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I284" s="2" t="n">
-        <v>1.85</v>
+        <v>1.81</v>
       </c>
       <c r="J284" s="2" t="s">
         <v>15</v>
@@ -11580,25 +11571,25 @@
         <v>10</v>
       </c>
       <c r="C285" s="2" t="s">
-        <v>467</v>
+        <v>464</v>
       </c>
       <c r="D285" s="2" t="s">
+        <v>597</v>
+      </c>
+      <c r="E285" s="2" t="s">
         <v>598</v>
       </c>
-      <c r="E285" s="2" t="s">
-        <v>599</v>
-      </c>
       <c r="F285" s="2" t="s">
-        <v>465</v>
+        <v>462</v>
       </c>
       <c r="G285" s="2" t="s">
-        <v>466</v>
+        <v>463</v>
       </c>
       <c r="H285" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I285" s="2" t="n">
-        <v>1.81</v>
+        <v>1.75</v>
       </c>
       <c r="J285" s="2" t="s">
         <v>15</v>
@@ -11609,28 +11600,28 @@
         <v>2023</v>
       </c>
       <c r="B286" s="2" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C286" s="2" t="s">
-        <v>467</v>
+        <v>471</v>
       </c>
       <c r="D286" s="2" t="s">
+        <v>599</v>
+      </c>
+      <c r="E286" s="2" t="s">
         <v>600</v>
       </c>
-      <c r="E286" s="2" t="s">
-        <v>601</v>
-      </c>
       <c r="F286" s="2" t="s">
-        <v>465</v>
+        <v>462</v>
       </c>
       <c r="G286" s="2" t="s">
-        <v>466</v>
+        <v>463</v>
       </c>
       <c r="H286" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I286" s="2" t="n">
-        <v>1.75</v>
+        <v>1.71</v>
       </c>
       <c r="J286" s="2" t="s">
         <v>15</v>
@@ -11641,28 +11632,28 @@
         <v>2023</v>
       </c>
       <c r="B287" s="2" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C287" s="2" t="s">
-        <v>474</v>
+        <v>459</v>
       </c>
       <c r="D287" s="2" t="s">
+        <v>601</v>
+      </c>
+      <c r="E287" s="2" t="s">
         <v>602</v>
       </c>
-      <c r="E287" s="2" t="s">
-        <v>603</v>
-      </c>
       <c r="F287" s="2" t="s">
-        <v>465</v>
+        <v>462</v>
       </c>
       <c r="G287" s="2" t="s">
-        <v>466</v>
+        <v>463</v>
       </c>
       <c r="H287" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I287" s="2" t="n">
-        <v>1.71</v>
+        <v>1.68</v>
       </c>
       <c r="J287" s="2" t="s">
         <v>15</v>
@@ -11676,25 +11667,25 @@
         <v>8</v>
       </c>
       <c r="C288" s="2" t="s">
+        <v>459</v>
+      </c>
+      <c r="D288" s="2" t="s">
+        <v>603</v>
+      </c>
+      <c r="E288" s="2" t="s">
+        <v>604</v>
+      </c>
+      <c r="F288" s="2" t="s">
         <v>462</v>
       </c>
-      <c r="D288" s="2" t="s">
-        <v>604</v>
-      </c>
-      <c r="E288" s="2" t="s">
-        <v>605</v>
-      </c>
-      <c r="F288" s="2" t="s">
-        <v>465</v>
-      </c>
       <c r="G288" s="2" t="s">
-        <v>466</v>
+        <v>463</v>
       </c>
       <c r="H288" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I288" s="2" t="n">
-        <v>1.68</v>
+        <v>1.67</v>
       </c>
       <c r="J288" s="2" t="s">
         <v>15</v>
@@ -11708,19 +11699,19 @@
         <v>8</v>
       </c>
       <c r="C289" s="2" t="s">
+        <v>459</v>
+      </c>
+      <c r="D289" s="2" t="s">
+        <v>605</v>
+      </c>
+      <c r="E289" s="2" t="s">
+        <v>606</v>
+      </c>
+      <c r="F289" s="2" t="s">
         <v>462</v>
       </c>
-      <c r="D289" s="2" t="s">
-        <v>606</v>
-      </c>
-      <c r="E289" s="2" t="s">
-        <v>607</v>
-      </c>
-      <c r="F289" s="2" t="s">
-        <v>465</v>
-      </c>
       <c r="G289" s="2" t="s">
-        <v>466</v>
+        <v>463</v>
       </c>
       <c r="H289" s="2" t="s">
         <v>15</v>
@@ -11737,28 +11728,28 @@
         <v>2023</v>
       </c>
       <c r="B290" s="2" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C290" s="2" t="s">
+        <v>471</v>
+      </c>
+      <c r="D290" s="2" t="s">
+        <v>607</v>
+      </c>
+      <c r="E290" s="2" t="s">
+        <v>608</v>
+      </c>
+      <c r="F290" s="2" t="s">
         <v>462</v>
       </c>
-      <c r="D290" s="2" t="s">
-        <v>608</v>
-      </c>
-      <c r="E290" s="2" t="s">
-        <v>609</v>
-      </c>
-      <c r="F290" s="2" t="s">
-        <v>465</v>
-      </c>
       <c r="G290" s="2" t="s">
-        <v>466</v>
+        <v>463</v>
       </c>
       <c r="H290" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I290" s="2" t="n">
-        <v>1.67</v>
+        <v>1.66</v>
       </c>
       <c r="J290" s="2" t="s">
         <v>15</v>
@@ -11769,28 +11760,28 @@
         <v>2023</v>
       </c>
       <c r="B291" s="2" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C291" s="2" t="s">
-        <v>474</v>
+        <v>459</v>
       </c>
       <c r="D291" s="2" t="s">
+        <v>609</v>
+      </c>
+      <c r="E291" s="2" t="s">
         <v>610</v>
       </c>
-      <c r="E291" s="2" t="s">
-        <v>611</v>
-      </c>
       <c r="F291" s="2" t="s">
-        <v>465</v>
+        <v>462</v>
       </c>
       <c r="G291" s="2" t="s">
-        <v>466</v>
+        <v>463</v>
       </c>
       <c r="H291" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I291" s="2" t="n">
-        <v>1.66</v>
+        <v>1.64</v>
       </c>
       <c r="J291" s="2" t="s">
         <v>15</v>
@@ -11801,22 +11792,22 @@
         <v>2023</v>
       </c>
       <c r="B292" s="2" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="C292" s="2" t="s">
+        <v>464</v>
+      </c>
+      <c r="D292" s="2" t="s">
+        <v>611</v>
+      </c>
+      <c r="E292" s="2" t="s">
+        <v>612</v>
+      </c>
+      <c r="F292" s="2" t="s">
         <v>462</v>
       </c>
-      <c r="D292" s="2" t="s">
-        <v>612</v>
-      </c>
-      <c r="E292" s="2" t="s">
-        <v>613</v>
-      </c>
-      <c r="F292" s="2" t="s">
-        <v>465</v>
-      </c>
       <c r="G292" s="2" t="s">
-        <v>466</v>
+        <v>463</v>
       </c>
       <c r="H292" s="2" t="s">
         <v>15</v>
@@ -11833,28 +11824,28 @@
         <v>2023</v>
       </c>
       <c r="B293" s="2" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="C293" s="2" t="s">
-        <v>467</v>
+        <v>459</v>
       </c>
       <c r="D293" s="2" t="s">
+        <v>613</v>
+      </c>
+      <c r="E293" s="2" t="s">
         <v>614</v>
       </c>
-      <c r="E293" s="2" t="s">
-        <v>615</v>
-      </c>
       <c r="F293" s="2" t="s">
-        <v>465</v>
+        <v>462</v>
       </c>
       <c r="G293" s="2" t="s">
-        <v>466</v>
+        <v>463</v>
       </c>
       <c r="H293" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I293" s="2" t="n">
-        <v>1.64</v>
+        <v>1.59</v>
       </c>
       <c r="J293" s="2" t="s">
         <v>15</v>
@@ -11865,28 +11856,28 @@
         <v>2023</v>
       </c>
       <c r="B294" s="2" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C294" s="2" t="s">
+        <v>471</v>
+      </c>
+      <c r="D294" s="2" t="s">
+        <v>615</v>
+      </c>
+      <c r="E294" s="2" t="s">
+        <v>616</v>
+      </c>
+      <c r="F294" s="2" t="s">
         <v>462</v>
       </c>
-      <c r="D294" s="2" t="s">
-        <v>616</v>
-      </c>
-      <c r="E294" s="2" t="s">
-        <v>617</v>
-      </c>
-      <c r="F294" s="2" t="s">
-        <v>465</v>
-      </c>
       <c r="G294" s="2" t="s">
-        <v>466</v>
+        <v>463</v>
       </c>
       <c r="H294" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I294" s="2" t="n">
-        <v>1.59</v>
+        <v>1.58</v>
       </c>
       <c r="J294" s="2" t="s">
         <v>15</v>
@@ -11900,25 +11891,25 @@
         <v>9</v>
       </c>
       <c r="C295" s="2" t="s">
-        <v>474</v>
+        <v>471</v>
       </c>
       <c r="D295" s="2" t="s">
+        <v>617</v>
+      </c>
+      <c r="E295" s="2" t="s">
         <v>618</v>
       </c>
-      <c r="E295" s="2" t="s">
-        <v>619</v>
-      </c>
       <c r="F295" s="2" t="s">
-        <v>465</v>
+        <v>462</v>
       </c>
       <c r="G295" s="2" t="s">
-        <v>466</v>
+        <v>463</v>
       </c>
       <c r="H295" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I295" s="2" t="n">
-        <v>1.58</v>
+        <v>1.57</v>
       </c>
       <c r="J295" s="2" t="s">
         <v>15</v>
@@ -11929,22 +11920,22 @@
         <v>2023</v>
       </c>
       <c r="B296" s="2" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C296" s="2" t="s">
-        <v>474</v>
+        <v>464</v>
       </c>
       <c r="D296" s="2" t="s">
+        <v>619</v>
+      </c>
+      <c r="E296" s="2" t="s">
         <v>620</v>
       </c>
-      <c r="E296" s="2" t="s">
-        <v>621</v>
-      </c>
       <c r="F296" s="2" t="s">
-        <v>465</v>
+        <v>462</v>
       </c>
       <c r="G296" s="2" t="s">
-        <v>466</v>
+        <v>463</v>
       </c>
       <c r="H296" s="2" t="s">
         <v>15</v>
@@ -11961,28 +11952,28 @@
         <v>2023</v>
       </c>
       <c r="B297" s="2" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="C297" s="2" t="s">
-        <v>467</v>
+        <v>459</v>
       </c>
       <c r="D297" s="2" t="s">
+        <v>621</v>
+      </c>
+      <c r="E297" s="2" t="s">
         <v>622</v>
       </c>
-      <c r="E297" s="2" t="s">
-        <v>623</v>
-      </c>
       <c r="F297" s="2" t="s">
-        <v>465</v>
+        <v>462</v>
       </c>
       <c r="G297" s="2" t="s">
-        <v>466</v>
+        <v>463</v>
       </c>
       <c r="H297" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I297" s="2" t="n">
-        <v>1.57</v>
+        <v>1.55</v>
       </c>
       <c r="J297" s="2" t="s">
         <v>15</v>
@@ -11993,22 +11984,22 @@
         <v>2023</v>
       </c>
       <c r="B298" s="2" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C298" s="2" t="s">
+        <v>471</v>
+      </c>
+      <c r="D298" s="2" t="s">
+        <v>623</v>
+      </c>
+      <c r="E298" s="2" t="s">
+        <v>624</v>
+      </c>
+      <c r="F298" s="2" t="s">
         <v>462</v>
       </c>
-      <c r="D298" s="2" t="s">
-        <v>624</v>
-      </c>
-      <c r="E298" s="2" t="s">
-        <v>625</v>
-      </c>
-      <c r="F298" s="2" t="s">
-        <v>465</v>
-      </c>
       <c r="G298" s="2" t="s">
-        <v>466</v>
+        <v>463</v>
       </c>
       <c r="H298" s="2" t="s">
         <v>15</v>
@@ -12028,25 +12019,25 @@
         <v>9</v>
       </c>
       <c r="C299" s="2" t="s">
-        <v>474</v>
+        <v>471</v>
       </c>
       <c r="D299" s="2" t="s">
+        <v>625</v>
+      </c>
+      <c r="E299" s="2" t="s">
         <v>626</v>
       </c>
-      <c r="E299" s="2" t="s">
-        <v>627</v>
-      </c>
       <c r="F299" s="2" t="s">
-        <v>465</v>
+        <v>462</v>
       </c>
       <c r="G299" s="2" t="s">
-        <v>466</v>
+        <v>463</v>
       </c>
       <c r="H299" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I299" s="2" t="n">
-        <v>1.55</v>
+        <v>1.54</v>
       </c>
       <c r="J299" s="2" t="s">
         <v>15</v>
@@ -12057,28 +12048,28 @@
         <v>2023</v>
       </c>
       <c r="B300" s="2" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C300" s="2" t="s">
-        <v>474</v>
+        <v>459</v>
       </c>
       <c r="D300" s="2" t="s">
+        <v>627</v>
+      </c>
+      <c r="E300" s="2" t="s">
         <v>628</v>
       </c>
-      <c r="E300" s="2" t="s">
-        <v>629</v>
-      </c>
       <c r="F300" s="2" t="s">
-        <v>465</v>
+        <v>462</v>
       </c>
       <c r="G300" s="2" t="s">
-        <v>466</v>
+        <v>463</v>
       </c>
       <c r="H300" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I300" s="2" t="n">
-        <v>1.54</v>
+        <v>1.53</v>
       </c>
       <c r="J300" s="2" t="s">
         <v>15</v>
@@ -12089,22 +12080,22 @@
         <v>2023</v>
       </c>
       <c r="B301" s="2" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="C301" s="2" t="s">
+        <v>464</v>
+      </c>
+      <c r="D301" s="2" t="s">
+        <v>629</v>
+      </c>
+      <c r="E301" s="2" t="s">
+        <v>630</v>
+      </c>
+      <c r="F301" s="2" t="s">
         <v>462</v>
       </c>
-      <c r="D301" s="2" t="s">
-        <v>630</v>
-      </c>
-      <c r="E301" s="2" t="s">
-        <v>631</v>
-      </c>
-      <c r="F301" s="2" t="s">
-        <v>465</v>
-      </c>
       <c r="G301" s="2" t="s">
-        <v>466</v>
+        <v>463</v>
       </c>
       <c r="H301" s="2" t="s">
         <v>15</v>
@@ -12121,28 +12112,28 @@
         <v>2023</v>
       </c>
       <c r="B302" s="2" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="C302" s="2" t="s">
-        <v>467</v>
+        <v>459</v>
       </c>
       <c r="D302" s="2" t="s">
+        <v>631</v>
+      </c>
+      <c r="E302" s="2" t="s">
         <v>632</v>
       </c>
-      <c r="E302" s="2" t="s">
-        <v>633</v>
-      </c>
       <c r="F302" s="2" t="s">
-        <v>465</v>
+        <v>462</v>
       </c>
       <c r="G302" s="2" t="s">
-        <v>466</v>
+        <v>463</v>
       </c>
       <c r="H302" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I302" s="2" t="n">
-        <v>1.53</v>
+        <v>1.52</v>
       </c>
       <c r="J302" s="2" t="s">
         <v>15</v>
@@ -12156,25 +12147,25 @@
         <v>8</v>
       </c>
       <c r="C303" s="2" t="s">
+        <v>459</v>
+      </c>
+      <c r="D303" s="2" t="s">
+        <v>633</v>
+      </c>
+      <c r="E303" s="2" t="s">
+        <v>634</v>
+      </c>
+      <c r="F303" s="2" t="s">
         <v>462</v>
       </c>
-      <c r="D303" s="2" t="s">
-        <v>634</v>
-      </c>
-      <c r="E303" s="2" t="s">
-        <v>635</v>
-      </c>
-      <c r="F303" s="2" t="s">
-        <v>465</v>
-      </c>
       <c r="G303" s="2" t="s">
-        <v>466</v>
+        <v>463</v>
       </c>
       <c r="H303" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I303" s="2" t="n">
-        <v>1.52</v>
+        <v>1.48</v>
       </c>
       <c r="J303" s="2" t="s">
         <v>15</v>
@@ -12185,28 +12176,28 @@
         <v>2023</v>
       </c>
       <c r="B304" s="2" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C304" s="2" t="s">
+        <v>471</v>
+      </c>
+      <c r="D304" s="2" t="s">
+        <v>635</v>
+      </c>
+      <c r="E304" s="2" t="s">
+        <v>636</v>
+      </c>
+      <c r="F304" s="2" t="s">
         <v>462</v>
       </c>
-      <c r="D304" s="2" t="s">
-        <v>636</v>
-      </c>
-      <c r="E304" s="2" t="s">
-        <v>637</v>
-      </c>
-      <c r="F304" s="2" t="s">
-        <v>465</v>
-      </c>
       <c r="G304" s="2" t="s">
-        <v>466</v>
+        <v>463</v>
       </c>
       <c r="H304" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I304" s="2" t="n">
-        <v>1.48</v>
+        <v>1.44</v>
       </c>
       <c r="J304" s="2" t="s">
         <v>15</v>
@@ -12220,25 +12211,25 @@
         <v>9</v>
       </c>
       <c r="C305" s="2" t="s">
-        <v>474</v>
+        <v>471</v>
       </c>
       <c r="D305" s="2" t="s">
+        <v>637</v>
+      </c>
+      <c r="E305" s="2" t="s">
         <v>638</v>
       </c>
-      <c r="E305" s="2" t="s">
-        <v>639</v>
-      </c>
       <c r="F305" s="2" t="s">
-        <v>465</v>
+        <v>462</v>
       </c>
       <c r="G305" s="2" t="s">
-        <v>466</v>
+        <v>463</v>
       </c>
       <c r="H305" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I305" s="2" t="n">
-        <v>1.44</v>
+        <v>1.43</v>
       </c>
       <c r="J305" s="2" t="s">
         <v>15</v>
@@ -12249,22 +12240,22 @@
         <v>2023</v>
       </c>
       <c r="B306" s="2" t="n">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="C306" s="2" t="s">
-        <v>474</v>
+        <v>492</v>
       </c>
       <c r="D306" s="2" t="s">
+        <v>639</v>
+      </c>
+      <c r="E306" s="2" t="s">
         <v>640</v>
       </c>
-      <c r="E306" s="2" t="s">
-        <v>641</v>
-      </c>
       <c r="F306" s="2" t="s">
-        <v>465</v>
+        <v>462</v>
       </c>
       <c r="G306" s="2" t="s">
-        <v>466</v>
+        <v>463</v>
       </c>
       <c r="H306" s="2" t="s">
         <v>15</v>
@@ -12281,28 +12272,28 @@
         <v>2023</v>
       </c>
       <c r="B307" s="2" t="n">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="C307" s="2" t="s">
-        <v>495</v>
+        <v>459</v>
       </c>
       <c r="D307" s="2" t="s">
+        <v>641</v>
+      </c>
+      <c r="E307" s="2" t="s">
         <v>642</v>
       </c>
-      <c r="E307" s="2" t="s">
-        <v>643</v>
-      </c>
       <c r="F307" s="2" t="s">
-        <v>465</v>
+        <v>462</v>
       </c>
       <c r="G307" s="2" t="s">
-        <v>466</v>
+        <v>463</v>
       </c>
       <c r="H307" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I307" s="2" t="n">
-        <v>1.43</v>
+        <v>1.42</v>
       </c>
       <c r="J307" s="2" t="s">
         <v>15</v>
@@ -12313,28 +12304,28 @@
         <v>2023</v>
       </c>
       <c r="B308" s="2" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C308" s="2" t="s">
+        <v>471</v>
+      </c>
+      <c r="D308" s="2" t="s">
+        <v>643</v>
+      </c>
+      <c r="E308" s="2" t="s">
+        <v>644</v>
+      </c>
+      <c r="F308" s="2" t="s">
         <v>462</v>
       </c>
-      <c r="D308" s="2" t="s">
-        <v>644</v>
-      </c>
-      <c r="E308" s="2" t="s">
-        <v>645</v>
-      </c>
-      <c r="F308" s="2" t="s">
-        <v>465</v>
-      </c>
       <c r="G308" s="2" t="s">
-        <v>466</v>
+        <v>463</v>
       </c>
       <c r="H308" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I308" s="2" t="n">
-        <v>1.42</v>
+        <v>1.41</v>
       </c>
       <c r="J308" s="2" t="s">
         <v>15</v>
@@ -12345,28 +12336,28 @@
         <v>2023</v>
       </c>
       <c r="B309" s="2" t="n">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="C309" s="2" t="s">
-        <v>474</v>
+        <v>492</v>
       </c>
       <c r="D309" s="2" t="s">
+        <v>645</v>
+      </c>
+      <c r="E309" s="2" t="s">
         <v>646</v>
       </c>
-      <c r="E309" s="2" t="s">
-        <v>647</v>
-      </c>
       <c r="F309" s="2" t="s">
-        <v>465</v>
+        <v>462</v>
       </c>
       <c r="G309" s="2" t="s">
-        <v>466</v>
+        <v>463</v>
       </c>
       <c r="H309" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I309" s="2" t="n">
-        <v>1.41</v>
+        <v>1.39</v>
       </c>
       <c r="J309" s="2" t="s">
         <v>15</v>
@@ -12380,25 +12371,25 @@
         <v>14</v>
       </c>
       <c r="C310" s="2" t="s">
-        <v>495</v>
+        <v>492</v>
       </c>
       <c r="D310" s="2" t="s">
-        <v>648</v>
+        <v>647</v>
       </c>
       <c r="E310" s="2" t="s">
-        <v>649</v>
+        <v>464</v>
       </c>
       <c r="F310" s="2" t="s">
-        <v>465</v>
+        <v>462</v>
       </c>
       <c r="G310" s="2" t="s">
-        <v>466</v>
+        <v>463</v>
       </c>
       <c r="H310" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I310" s="2" t="n">
-        <v>1.39</v>
+        <v>1.38</v>
       </c>
       <c r="J310" s="2" t="s">
         <v>15</v>
@@ -12409,28 +12400,28 @@
         <v>2023</v>
       </c>
       <c r="B311" s="2" t="n">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="C311" s="2" t="s">
-        <v>495</v>
+        <v>459</v>
       </c>
       <c r="D311" s="2" t="s">
-        <v>650</v>
+        <v>648</v>
       </c>
       <c r="E311" s="2" t="s">
-        <v>467</v>
+        <v>649</v>
       </c>
       <c r="F311" s="2" t="s">
-        <v>465</v>
+        <v>462</v>
       </c>
       <c r="G311" s="2" t="s">
-        <v>466</v>
+        <v>463</v>
       </c>
       <c r="H311" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I311" s="2" t="n">
-        <v>1.38</v>
+        <v>1.37</v>
       </c>
       <c r="J311" s="2" t="s">
         <v>15</v>
@@ -12444,25 +12435,25 @@
         <v>8</v>
       </c>
       <c r="C312" s="2" t="s">
+        <v>459</v>
+      </c>
+      <c r="D312" s="2" t="s">
+        <v>650</v>
+      </c>
+      <c r="E312" s="2" t="s">
+        <v>651</v>
+      </c>
+      <c r="F312" s="2" t="s">
         <v>462</v>
       </c>
-      <c r="D312" s="2" t="s">
-        <v>651</v>
-      </c>
-      <c r="E312" s="2" t="s">
-        <v>652</v>
-      </c>
-      <c r="F312" s="2" t="s">
-        <v>465</v>
-      </c>
       <c r="G312" s="2" t="s">
-        <v>466</v>
+        <v>463</v>
       </c>
       <c r="H312" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I312" s="2" t="n">
-        <v>1.37</v>
+        <v>1.36</v>
       </c>
       <c r="J312" s="2" t="s">
         <v>15</v>
@@ -12473,28 +12464,28 @@
         <v>2023</v>
       </c>
       <c r="B313" s="2" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C313" s="2" t="s">
+        <v>471</v>
+      </c>
+      <c r="D313" s="2" t="s">
+        <v>652</v>
+      </c>
+      <c r="E313" s="2" t="s">
+        <v>653</v>
+      </c>
+      <c r="F313" s="2" t="s">
         <v>462</v>
       </c>
-      <c r="D313" s="2" t="s">
-        <v>653</v>
-      </c>
-      <c r="E313" s="2" t="s">
-        <v>654</v>
-      </c>
-      <c r="F313" s="2" t="s">
-        <v>465</v>
-      </c>
       <c r="G313" s="2" t="s">
-        <v>466</v>
+        <v>463</v>
       </c>
       <c r="H313" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I313" s="2" t="n">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="J313" s="2" t="s">
         <v>15</v>
@@ -12505,28 +12496,28 @@
         <v>2023</v>
       </c>
       <c r="B314" s="2" t="n">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="C314" s="2" t="s">
-        <v>474</v>
+        <v>492</v>
       </c>
       <c r="D314" s="2" t="s">
+        <v>654</v>
+      </c>
+      <c r="E314" s="2" t="s">
         <v>655</v>
       </c>
-      <c r="E314" s="2" t="s">
-        <v>656</v>
-      </c>
       <c r="F314" s="2" t="s">
-        <v>465</v>
+        <v>462</v>
       </c>
       <c r="G314" s="2" t="s">
-        <v>466</v>
+        <v>463</v>
       </c>
       <c r="H314" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I314" s="2" t="n">
-        <v>1.35</v>
+        <v>1.31</v>
       </c>
       <c r="J314" s="2" t="s">
         <v>15</v>
@@ -12537,28 +12528,28 @@
         <v>2023</v>
       </c>
       <c r="B315" s="2" t="n">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="C315" s="2" t="s">
-        <v>495</v>
+        <v>459</v>
       </c>
       <c r="D315" s="2" t="s">
+        <v>656</v>
+      </c>
+      <c r="E315" s="2" t="s">
         <v>657</v>
       </c>
-      <c r="E315" s="2" t="s">
-        <v>658</v>
-      </c>
       <c r="F315" s="2" t="s">
-        <v>465</v>
+        <v>462</v>
       </c>
       <c r="G315" s="2" t="s">
-        <v>466</v>
+        <v>463</v>
       </c>
       <c r="H315" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I315" s="2" t="n">
-        <v>1.31</v>
+        <v>1.28</v>
       </c>
       <c r="J315" s="2" t="s">
         <v>15</v>
@@ -12569,28 +12560,28 @@
         <v>2023</v>
       </c>
       <c r="B316" s="2" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="C316" s="2" t="s">
+        <v>464</v>
+      </c>
+      <c r="D316" s="2" t="s">
+        <v>658</v>
+      </c>
+      <c r="E316" s="2" t="s">
+        <v>659</v>
+      </c>
+      <c r="F316" s="2" t="s">
         <v>462</v>
       </c>
-      <c r="D316" s="2" t="s">
-        <v>659</v>
-      </c>
-      <c r="E316" s="2" t="s">
-        <v>660</v>
-      </c>
-      <c r="F316" s="2" t="s">
-        <v>465</v>
-      </c>
       <c r="G316" s="2" t="s">
-        <v>466</v>
+        <v>463</v>
       </c>
       <c r="H316" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I316" s="2" t="n">
-        <v>1.28</v>
+        <v>1.25</v>
       </c>
       <c r="J316" s="2" t="s">
         <v>15</v>
@@ -12601,28 +12592,28 @@
         <v>2023</v>
       </c>
       <c r="B317" s="2" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C317" s="2" t="s">
-        <v>467</v>
+        <v>471</v>
       </c>
       <c r="D317" s="2" t="s">
+        <v>660</v>
+      </c>
+      <c r="E317" s="2" t="s">
         <v>661</v>
       </c>
-      <c r="E317" s="2" t="s">
-        <v>662</v>
-      </c>
       <c r="F317" s="2" t="s">
-        <v>465</v>
+        <v>462</v>
       </c>
       <c r="G317" s="2" t="s">
-        <v>466</v>
+        <v>463</v>
       </c>
       <c r="H317" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I317" s="2" t="n">
-        <v>1.25</v>
+        <v>1.23</v>
       </c>
       <c r="J317" s="2" t="s">
         <v>15</v>
@@ -12636,25 +12627,25 @@
         <v>9</v>
       </c>
       <c r="C318" s="2" t="s">
-        <v>474</v>
+        <v>471</v>
       </c>
       <c r="D318" s="2" t="s">
+        <v>662</v>
+      </c>
+      <c r="E318" s="2" t="s">
         <v>663</v>
       </c>
-      <c r="E318" s="2" t="s">
-        <v>664</v>
-      </c>
       <c r="F318" s="2" t="s">
-        <v>465</v>
+        <v>462</v>
       </c>
       <c r="G318" s="2" t="s">
-        <v>466</v>
+        <v>463</v>
       </c>
       <c r="H318" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I318" s="2" t="n">
-        <v>1.23</v>
+        <v>1.21</v>
       </c>
       <c r="J318" s="2" t="s">
         <v>15</v>
@@ -12668,25 +12659,25 @@
         <v>9</v>
       </c>
       <c r="C319" s="2" t="s">
-        <v>474</v>
+        <v>471</v>
       </c>
       <c r="D319" s="2" t="s">
+        <v>664</v>
+      </c>
+      <c r="E319" s="2" t="s">
         <v>665</v>
       </c>
-      <c r="E319" s="2" t="s">
-        <v>666</v>
-      </c>
       <c r="F319" s="2" t="s">
-        <v>465</v>
+        <v>462</v>
       </c>
       <c r="G319" s="2" t="s">
-        <v>466</v>
+        <v>463</v>
       </c>
       <c r="H319" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I319" s="2" t="n">
-        <v>1.21</v>
+        <v>1.15</v>
       </c>
       <c r="J319" s="2" t="s">
         <v>15</v>
@@ -12697,28 +12688,28 @@
         <v>2023</v>
       </c>
       <c r="B320" s="2" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C320" s="2" t="s">
-        <v>474</v>
+        <v>459</v>
       </c>
       <c r="D320" s="2" t="s">
+        <v>666</v>
+      </c>
+      <c r="E320" s="2" t="s">
         <v>667</v>
       </c>
-      <c r="E320" s="2" t="s">
-        <v>668</v>
-      </c>
       <c r="F320" s="2" t="s">
-        <v>465</v>
+        <v>462</v>
       </c>
       <c r="G320" s="2" t="s">
-        <v>466</v>
+        <v>463</v>
       </c>
       <c r="H320" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I320" s="2" t="n">
-        <v>1.15</v>
+        <v>1.13</v>
       </c>
       <c r="J320" s="2" t="s">
         <v>15</v>
@@ -12732,25 +12723,25 @@
         <v>8</v>
       </c>
       <c r="C321" s="2" t="s">
+        <v>459</v>
+      </c>
+      <c r="D321" s="2" t="s">
+        <v>668</v>
+      </c>
+      <c r="E321" s="2" t="s">
+        <v>669</v>
+      </c>
+      <c r="F321" s="2" t="s">
         <v>462</v>
       </c>
-      <c r="D321" s="2" t="s">
-        <v>669</v>
-      </c>
-      <c r="E321" s="2" t="s">
-        <v>670</v>
-      </c>
-      <c r="F321" s="2" t="s">
-        <v>465</v>
-      </c>
       <c r="G321" s="2" t="s">
-        <v>466</v>
+        <v>463</v>
       </c>
       <c r="H321" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I321" s="2" t="n">
-        <v>1.13</v>
+        <v>1.12</v>
       </c>
       <c r="J321" s="2" t="s">
         <v>15</v>
@@ -12761,28 +12752,28 @@
         <v>2023</v>
       </c>
       <c r="B322" s="2" t="n">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="C322" s="2" t="s">
+        <v>492</v>
+      </c>
+      <c r="D322" s="2" t="s">
+        <v>670</v>
+      </c>
+      <c r="E322" s="2" t="s">
+        <v>671</v>
+      </c>
+      <c r="F322" s="2" t="s">
         <v>462</v>
       </c>
-      <c r="D322" s="2" t="s">
-        <v>671</v>
-      </c>
-      <c r="E322" s="2" t="s">
-        <v>672</v>
-      </c>
-      <c r="F322" s="2" t="s">
-        <v>465</v>
-      </c>
       <c r="G322" s="2" t="s">
-        <v>466</v>
+        <v>463</v>
       </c>
       <c r="H322" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I322" s="2" t="n">
-        <v>1.12</v>
+        <v>1.1</v>
       </c>
       <c r="J322" s="2" t="s">
         <v>15</v>
@@ -12796,25 +12787,25 @@
         <v>14</v>
       </c>
       <c r="C323" s="2" t="s">
-        <v>495</v>
+        <v>492</v>
       </c>
       <c r="D323" s="2" t="s">
+        <v>672</v>
+      </c>
+      <c r="E323" s="2" t="s">
         <v>673</v>
       </c>
-      <c r="E323" s="2" t="s">
-        <v>674</v>
-      </c>
       <c r="F323" s="2" t="s">
-        <v>465</v>
+        <v>462</v>
       </c>
       <c r="G323" s="2" t="s">
-        <v>466</v>
+        <v>463</v>
       </c>
       <c r="H323" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I323" s="2" t="n">
-        <v>1.1</v>
+        <v>1.04</v>
       </c>
       <c r="J323" s="2" t="s">
         <v>15</v>
@@ -12825,67 +12816,35 @@
         <v>2023</v>
       </c>
       <c r="B324" s="2" t="n">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="C324" s="2" t="s">
-        <v>495</v>
+        <v>459</v>
       </c>
       <c r="D324" s="2" t="s">
+        <v>674</v>
+      </c>
+      <c r="E324" s="2" t="s">
         <v>675</v>
       </c>
-      <c r="E324" s="2" t="s">
-        <v>676</v>
-      </c>
       <c r="F324" s="2" t="s">
-        <v>465</v>
+        <v>462</v>
       </c>
       <c r="G324" s="2" t="s">
-        <v>466</v>
+        <v>463</v>
       </c>
       <c r="H324" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I324" s="2" t="n">
-        <v>1.04</v>
+        <v>0.93</v>
       </c>
       <c r="J324" s="2" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="325">
-      <c r="A325" s="2" t="n">
-        <v>2023</v>
-      </c>
-      <c r="B325" s="2" t="n">
-        <v>8</v>
-      </c>
-      <c r="C325" s="2" t="s">
-        <v>462</v>
-      </c>
-      <c r="D325" s="2" t="s">
-        <v>677</v>
-      </c>
-      <c r="E325" s="2" t="s">
-        <v>678</v>
-      </c>
-      <c r="F325" s="2" t="s">
-        <v>465</v>
-      </c>
-      <c r="G325" s="2" t="s">
-        <v>466</v>
-      </c>
-      <c r="H325" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="I325" s="2" t="n">
-        <v>0.93</v>
-      </c>
-      <c r="J325" s="2" t="s">
-        <v>15</v>
-      </c>
-    </row>
   </sheetData>
-  <autoFilter ref="A1:J325"/>
+  <autoFilter ref="A1:J324"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>
 </worksheet>
@@ -12902,7 +12861,7 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>679</v>
+        <v>676</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>8</v>
@@ -12910,50 +12869,50 @@
     </row>
     <row r="2">
       <c r="A2" s="2" t="s">
-        <v>680</v>
+        <v>677</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>681</v>
+        <v>678</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="s">
-        <v>682</v>
+        <v>679</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>683</v>
+        <v>680</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="s">
-        <v>684</v>
+        <v>681</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>685</v>
+        <v>682</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="s">
-        <v>686</v>
+        <v>683</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>687</v>
+        <v>684</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="s">
-        <v>688</v>
+        <v>685</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>689</v>
+        <v>686</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="s">
-        <v>690</v>
+        <v>687</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>691</v>
+        <v>688</v>
       </c>
     </row>
   </sheetData>
@@ -12975,21 +12934,21 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>692</v>
+        <v>689</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>693</v>
+        <v>690</v>
       </c>
       <c r="C1" s="1" t="s">
         <v>0</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>694</v>
+        <v>691</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="s">
-        <v>695</v>
+        <v>692</v>
       </c>
       <c r="B2" s="2" t="s">
         <v>15</v>
@@ -12998,7 +12957,7 @@
         <v>2023</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>696</v>
+        <v>693</v>
       </c>
     </row>
   </sheetData>

--- a/output/graficos_nacionales/plot_nacional_e_rezjov_a_2023.xlsx
+++ b/output/graficos_nacionales/plot_nacional_e_rezjov_a_2023.xlsx
@@ -2053,7 +2053,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-07 12:58</t>
+    <t xml:space="preserve">2026-09-08 10:28</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
